--- a/out_FPT/lv_kpis_fpt.xlsx
+++ b/out_FPT/lv_kpis_fpt.xlsx
@@ -413,301 +413,311 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG33"/>
+  <dimension ref="A1:BI44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Pair_ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Pair_Label</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Fuel_Label</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>RPM</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Speed_RPM</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Power_kW</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Consumo_kg_h</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Power_kW_sd</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Consumo_kg_h_sd</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>N_points</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Source_Files</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Fuel_Density_kg_m3</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Fuel_Cost_R_L</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>LHV_kJ_kg</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Consumo_L_h</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Custo_R_h</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>n_th</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>n_th_pct</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Diesel_Baseline_Consumo_kg_h</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Diesel_Baseline_Consumo_L_h</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Diesel_Baseline_Custo_R_h</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Diesel_Baseline_n_th_pct</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Diesel_Baseline_Power_kW</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_h</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_pct</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Delta_Consumo_kg_h_vs_Diesel</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Delta_Consumo_L_h_vs_Diesel</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Delta_n_th_pct_vs_Diesel</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_Hours_Ano</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_Diesel_L_h</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_Diesel_L_ano</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_Diesel_Custo_R_h</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_Diesel_Custo_R_ano</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_E94H6_L_h</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_E94H6_L_ano</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_E94H6_Custo_R_h</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_E94H6_Custo_R_ano</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_Economia_R_h</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_Economia_R_ano</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_Hours_Ano</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_Diesel_L_h</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_Diesel_L_ano</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_Diesel_Custo_R_h</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_Diesel_Custo_R_ano</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_E94H6_L_h</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_E94H6_L_ano</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_E94H6_Custo_R_h</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_E94H6_Custo_R_ano</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_Economia_R_h</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_Economia_R_ano</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_Hours_Ano</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_Diesel_L_h</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_Diesel_L_ano</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_Diesel_Custo_R_h</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_Diesel_Custo_R_ano</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_E94H6_L_h</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_E94H6_L_ano</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_E94H6_Custo_R_h</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_E94H6_Custo_R_ano</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_Economia_R_h</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_Economia_R_ano</t>
         </is>
@@ -716,73 +726,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>900</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>899.994</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>70.07034</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>16.539</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>853</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>5.4</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>41600</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>19.38921453692849</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>104.7017584994138</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.3666351909472714</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>36.66351909472714</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>16.539</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>19.38921453692849</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>104.7017584994138</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>36.66351909472714</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>70.07034</v>
       </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
@@ -792,8 +806,12 @@
       <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
@@ -825,77 +843,83 @@
       <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>1001</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>1000.92</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>86.5329</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>19.382</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>853</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>5.4</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>41600</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>22.7221570926143</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>122.6996483001172</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.3863597171840645</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>38.63597171840645</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>19.382</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>22.7221570926143</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>122.6996483001172</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>38.63597171840645</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>86.5329</v>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
@@ -905,8 +929,12 @@
       <c r="Z3" t="n">
         <v>0</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
@@ -938,77 +966,83 @@
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>1100</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>1100.019</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>101.5714</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>21.938</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>853</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>5.4</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>41600</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>25.71864009378664</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>138.8806565064478</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.4006670021108439</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>40.06670021108439</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>21.938</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>25.71864009378664</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>138.8806565064478</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>40.06670021108439</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>101.5714</v>
       </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
@@ -1018,8 +1052,12 @@
       <c r="Z4" t="n">
         <v>0</v>
       </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
@@ -1051,77 +1089,83 @@
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>1200</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>1199.906</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>112.8476</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>24.062</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>853</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>5.4</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>41600</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>28.20867526377491</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>152.3268464243845</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.4058539478143002</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>40.58539478143002</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>24.062</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>28.20867526377491</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>152.3268464243845</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>40.58539478143002</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>112.8476</v>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
@@ -1131,8 +1175,12 @@
       <c r="Z5" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
@@ -1164,77 +1212,83 @@
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>1300</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>1300</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>126.6131</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>26.415</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>853</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>5.4</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>41600</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>30.96717467760844</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>167.2227432590856</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.4147985191980082</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>41.47985191980082</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>26.415</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>30.96717467760844</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>167.2227432590856</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>41.47985191980082</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>126.6131</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
@@ -1244,8 +1298,12 @@
       <c r="Z6" t="n">
         <v>0</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
@@ -1277,77 +1335,83 @@
       <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>1400</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>1400.01</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>142.0559</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>29.065</v>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>853</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>5.4</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>41600</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>34.07385697538101</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>183.9988276670574</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.4229588521748336</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>42.29588521748337</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>29.065</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>34.07385697538101</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>183.9988276670574</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>42.29588521748337</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>142.0559</v>
       </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
@@ -1357,8 +1421,12 @@
       <c r="Z7" t="n">
         <v>0</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
@@ -1390,77 +1458,83 @@
       <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>1500</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>1500.01</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>158.5028</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>32.921</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>853</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>5.4</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>41600</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>38.59437280187574</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>208.409613130129</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.416651634565732</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>41.6651634565732</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>32.921</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>38.59437280187574</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>208.409613130129</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>41.6651634565732</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>158.5028</v>
       </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
@@ -1470,8 +1544,12 @@
       <c r="Z8" t="n">
         <v>0</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
@@ -1503,77 +1581,83 @@
       <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>1600</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>1600.044</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>168.0404</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>34.72</v>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>853</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>5.4</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>41600</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>40.70339976553341</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>219.7983587338804</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>0.418835186990429</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>41.8835186990429</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>34.72</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>40.70339976553341</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>219.7983587338804</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>41.8835186990429</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>168.0404</v>
       </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
@@ -1583,8 +1667,12 @@
       <c r="Z9" t="n">
         <v>0</v>
       </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
@@ -1616,77 +1704,83 @@
       <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>1700</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>1699.996</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>178.8622</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>36.915</v>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>853</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>5.4</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>41600</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>43.27667057444314</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>233.694021101993</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>0.4193000031256838</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>41.93000031256837</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>36.915</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>43.27667057444314</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>233.694021101993</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>41.93000031256837</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>178.8622</v>
       </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
@@ -1696,8 +1790,12 @@
       <c r="Z10" t="n">
         <v>0</v>
       </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
@@ -1729,77 +1827,83 @@
       <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>1800</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>1799.969</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>189.4811</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>39.393</v>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>853</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>5.4</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>41600</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>46.18171160609613</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>249.3812426729191</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>0.4162516915344194</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>41.62516915344194</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>39.393</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>46.18171160609613</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>249.3812426729191</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>41.62516915344194</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>189.4811</v>
       </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
@@ -1809,8 +1913,12 @@
       <c r="Z11" t="n">
         <v>0</v>
       </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
@@ -1842,77 +1950,83 @@
       <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="D12" t="n">
         <v>1900</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>1899.985</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>199.5484</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>41.813</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>853</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>5.4</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>41600</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>49.01875732708089</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>264.7012895662368</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.4129962341487465</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>41.29962341487465</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>41.813</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>49.01875732708089</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>264.7012895662368</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>41.29962341487465</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>199.5484</v>
       </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
@@ -1922,8 +2036,12 @@
       <c r="Z12" t="n">
         <v>0</v>
       </c>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
@@ -1955,77 +2073,83 @@
       <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="D13" t="n">
         <v>2000</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>1999.993</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>205.9202</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>43.791</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>853</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>5.4</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>41600</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>51.33763188745603</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>277.2232121922626</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>0.4069333266582701</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>40.69333266582701</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>43.791</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>51.33763188745603</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>277.2232121922626</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>40.69333266582701</v>
       </c>
-      <c r="U13" t="n">
+      <c r="W13" t="n">
         <v>205.9202</v>
       </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
@@ -2035,8 +2159,12 @@
       <c r="Z13" t="n">
         <v>0</v>
       </c>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
@@ -2068,77 +2196,83 @@
       <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="inlineStr"/>
       <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="D14" t="n">
         <v>2100</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>2100.011</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>190.74</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>40.444</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>853</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>5.4</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>41600</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>47.41383352872216</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>256.0347010550997</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>0.4081284282921114</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>40.81284282921114</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>40.444</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>47.41383352872216</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>256.0347010550997</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>40.81284282921114</v>
       </c>
-      <c r="U14" t="n">
+      <c r="W14" t="n">
         <v>190.74</v>
       </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
@@ -2148,8 +2282,12 @@
       <c r="Z14" t="n">
         <v>0</v>
       </c>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
@@ -2181,77 +2319,83 @@
       <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="inlineStr"/>
       <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="D15" t="n">
         <v>2200</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>2199.961</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>180.1196</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>39.015</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>853</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>5.4</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>41600</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>45.73856975381008</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>246.9882766705745</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>0.3995200070978618</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>39.95200070978618</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>39.015</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>45.73856975381008</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>246.9882766705745</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>39.95200070978618</v>
       </c>
-      <c r="U15" t="n">
+      <c r="W15" t="n">
         <v>180.1196</v>
       </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
@@ -2261,8 +2405,12 @@
       <c r="Z15" t="n">
         <v>0</v>
       </c>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
@@ -2294,77 +2442,83 @@
       <c r="BE15" t="inlineStr"/>
       <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="D16" t="n">
         <v>2300</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>2299.989</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>174.8784</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>38.98</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>853</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>5.4</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>41600</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>45.69753810082063</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>246.7667057444314</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>0.3882428858980937</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>38.82428858980938</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>38.98</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>45.69753810082063</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>246.7667057444314</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>38.82428858980938</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>174.8784</v>
       </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
@@ -2374,8 +2528,12 @@
       <c r="Z16" t="n">
         <v>0</v>
       </c>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
@@ -2407,77 +2565,83 @@
       <c r="BE16" t="inlineStr"/>
       <c r="BF16" t="inlineStr"/>
       <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="D17" t="n">
         <v>2400</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>2400.038</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>171.4479</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>38.825</v>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="n">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>853</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>5.4</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>41600</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>45.5158264947245</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>245.7854630715123</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>0.3821464906632324</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>38.21464906632324</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>38.825</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>45.5158264947245</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>245.7854630715123</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>38.21464906632324</v>
       </c>
-      <c r="U17" t="n">
+      <c r="W17" t="n">
         <v>171.4479</v>
       </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
@@ -2487,8 +2651,12 @@
       <c r="Z17" t="n">
         <v>0</v>
       </c>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
@@ -2520,77 +2688,83 @@
       <c r="BE17" t="inlineStr"/>
       <c r="BF17" t="inlineStr"/>
       <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="D18" t="n">
         <v>2500</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>2500.012</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>169.3499</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>40.551</v>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="n">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>853</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>5.4</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>41600</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>47.53927315357561</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>256.7120750293083</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.361403659778854</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>36.14036597788539</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>40.551</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>47.53927315357561</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>256.7120750293083</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>36.14036597788539</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>169.3499</v>
       </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
@@ -2600,8 +2774,12 @@
       <c r="Z18" t="n">
         <v>0</v>
       </c>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
@@ -2633,77 +2811,83 @@
       <c r="BE18" t="inlineStr"/>
       <c r="BF18" t="inlineStr"/>
       <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>D85B15</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="D19" t="n">
         <v>2600</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>2599.939</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>97.5346</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>26.537</v>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="n">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15.xlsx</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>853</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>5.4</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>41600</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>31.11019929660024</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>167.9950762016413</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>0.3180651253257426</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>31.80651253257426</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>26.537</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>31.11019929660024</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>167.9950762016413</v>
       </c>
-      <c r="T19" t="n">
+      <c r="V19" t="n">
         <v>31.80651253257426</v>
       </c>
-      <c r="U19" t="n">
+      <c r="W19" t="n">
         <v>97.5346</v>
       </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
@@ -2713,8 +2897,12 @@
       <c r="Z19" t="n">
         <v>0</v>
       </c>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
@@ -2746,58 +2934,68 @@
       <c r="BE19" t="inlineStr"/>
       <c r="BF19" t="inlineStr"/>
       <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>E94H6</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="D20" t="n">
         <v>850</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>849.939</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>69.54826</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>30.775</v>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="n">
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6.xlsx</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>809</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>2.1</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>24600</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>38.04079110012361</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>79.88566131025958</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>0.3307163004497632</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>33.07163004497632</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -2839,58 +3037,68 @@
       <c r="BE20" t="inlineStr"/>
       <c r="BF20" t="inlineStr"/>
       <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>E94H6</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="D21" t="n">
         <v>1000</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>999.9450000000001</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>90.9374</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>35.783</v>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="n">
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6.xlsx</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>809</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>2.1</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>24600</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>44.23114956736712</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>92.88541409147095</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>0.371905994330323</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>37.1905994330323</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -2932,2154 +3140,3409 @@
       <c r="BE21" t="inlineStr"/>
       <c r="BF21" t="inlineStr"/>
       <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>E94H6</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="D22" t="n">
         <v>1100</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>1099.978</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>100.54</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>40.794</v>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="n">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6.xlsx</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>809</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>2.1</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>24600</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>50.42521631644005</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>105.8929542645241</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>0.3606699694000912</v>
       </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
         <v>36.06699694000912</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>21.938</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>25.71864009378664</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>138.8806565064478</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>40.06670021108439</v>
       </c>
-      <c r="U22" t="n">
+      <c r="W22" t="n">
         <v>101.5714</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>-32.98770224192374</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>-23.75255350293668</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>18.856</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>24.70657622265341</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
         <v>-3.999703271075269</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>3150</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>34</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AE22" t="n">
         <v>107100</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AF22" t="n">
         <v>183.6</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AG22" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AH22" t="n">
         <v>66.6620532231468</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>209985.4676529124</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AJ22" t="n">
         <v>139.9903117686083</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AK22" t="n">
         <v>440969.4820711161</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AL22" t="n">
         <v>-43.60968823139174</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AM22" t="n">
         <v>-137370.517928884</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AN22" t="n">
         <v>1675</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AO22" t="n">
         <v>12.1</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AP22" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AO22" t="n">
+      <c r="AQ22" t="n">
         <v>65.34</v>
       </c>
-      <c r="AP22" t="n">
+      <c r="AR22" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AS22" t="n">
         <v>23.72384835294342</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="AT22" t="n">
         <v>39737.44599118023</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AU22" t="n">
         <v>49.82008154118117</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AV22" t="n">
         <v>83448.63658147847</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AW22" t="n">
         <v>-15.51991845881883</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AX22" t="n">
         <v>-25995.86341852153</v>
       </c>
-      <c r="AW22" t="n">
+      <c r="AY22" t="n">
         <v>4800</v>
       </c>
-      <c r="AX22" t="n">
+      <c r="AZ22" t="n">
         <v>41</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="BA22" t="n">
         <v>196800</v>
       </c>
-      <c r="AZ22" t="n">
+      <c r="BB22" t="n">
         <v>221.4</v>
       </c>
-      <c r="BA22" t="n">
+      <c r="BC22" t="n">
         <v>1062720</v>
       </c>
-      <c r="BB22" t="n">
+      <c r="BD22" t="n">
         <v>80.38659359261818</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BE22" t="n">
         <v>385855.6492445673</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BF22" t="n">
         <v>168.8118465444982</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BG22" t="n">
         <v>810296.8634135913</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BH22" t="n">
         <v>-52.58815345550181</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BI22" t="n">
         <v>-252423.1365864087</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>E94H6</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="D23" t="n">
         <v>1200</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>1199.915</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>110.5485</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>43.955</v>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="n">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6.xlsx</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>809</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>2.1</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>24600</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>54.33250927070458</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>114.0982694684796</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>0.3680543571446407</v>
       </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
         <v>36.80543571446407</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>24.062</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>28.20867526377491</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>152.3268464243845</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
         <v>40.58539478143002</v>
       </c>
-      <c r="U23" t="n">
+      <c r="W23" t="n">
         <v>112.8476</v>
       </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
         <v>-38.22857695590493</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Y23" t="n">
         <v>-25.09641461978385</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>19.893</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>26.12383400692967</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>-3.779959066965944</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>3150</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>34</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AE23" t="n">
         <v>107100</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AF23" t="n">
         <v>183.6</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AG23" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AH23" t="n">
         <v>65.48713464670327</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>206284.4741371153</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AJ23" t="n">
         <v>137.5229827580769</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AK23" t="n">
         <v>433197.3956879421</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AL23" t="n">
         <v>-46.07701724192316</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AM23" t="n">
         <v>-145142.604312058</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AN23" t="n">
         <v>1675</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AO23" t="n">
         <v>12.1</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AP23" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AQ23" t="n">
         <v>65.34</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AR23" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AS23" t="n">
         <v>23.3057155654444</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AT23" t="n">
         <v>39037.07357211937</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AU23" t="n">
         <v>48.94200268743324</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AV23" t="n">
         <v>81977.85450145067</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AW23" t="n">
         <v>-16.39799731256677</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AX23" t="n">
         <v>-27466.64549854933</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="AY23" t="n">
         <v>4800</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="AZ23" t="n">
         <v>41</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="BA23" t="n">
         <v>196800</v>
       </c>
-      <c r="AZ23" t="n">
+      <c r="BB23" t="n">
         <v>221.4</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BC23" t="n">
         <v>1062720</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BD23" t="n">
         <v>78.96978001514218</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BE23" t="n">
         <v>379054.9440726825</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BF23" t="n">
         <v>165.8365380317986</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BG23" t="n">
         <v>796015.3825526332</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BH23" t="n">
         <v>-55.56346196820144</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BI23" t="n">
         <v>-266704.6174473668</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>E94H6</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="D24" t="n">
         <v>1300</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>1299.975</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>122.4565</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>47.414</v>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="n">
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6.xlsx</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>809</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>2.1</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>24600</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>58.60815822002472</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>123.0771322620519</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>0.3779572154771618</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>37.79572154771618</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>26.415</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>30.96717467760844</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>167.2227432590856</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>41.47985191980082</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>126.6131</v>
       </c>
-      <c r="V24" t="n">
+      <c r="X24" t="n">
         <v>-44.14561099703366</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Y24" t="n">
         <v>-26.39928644672269</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Z24" t="n">
         <v>20.999</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>27.64098354241628</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
         <v>-3.684130372084645</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>3150</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>34</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AE24" t="n">
         <v>107100</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AF24" t="n">
         <v>183.6</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AG24" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AH24" t="n">
         <v>64.34805242086532</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>202696.3651257257</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AJ24" t="n">
         <v>135.1309100838172</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AK24" t="n">
         <v>425662.366764024</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AL24" t="n">
         <v>-48.46908991618287</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AM24" t="n">
         <v>-152677.6332359761</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AN24" t="n">
         <v>1675</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AO24" t="n">
         <v>12.1</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AP24" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AO24" t="n">
+      <c r="AQ24" t="n">
         <v>65.34</v>
       </c>
-      <c r="AP24" t="n">
+      <c r="AR24" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AS24" t="n">
         <v>22.90033630271971</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AT24" t="n">
         <v>38358.06330705552</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AU24" t="n">
         <v>48.09070623571139</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="AV24" t="n">
         <v>80551.93294481658</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AW24" t="n">
         <v>-17.24929376428861</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AX24" t="n">
         <v>-28892.56705518342</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="AY24" t="n">
         <v>4800</v>
       </c>
-      <c r="AX24" t="n">
+      <c r="AZ24" t="n">
         <v>41</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="BA24" t="n">
         <v>196800</v>
       </c>
-      <c r="AZ24" t="n">
+      <c r="BB24" t="n">
         <v>221.4</v>
       </c>
-      <c r="BA24" t="n">
+      <c r="BC24" t="n">
         <v>1062720</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BD24" t="n">
         <v>77.59618086045522</v>
       </c>
-      <c r="BC24" t="n">
+      <c r="BE24" t="n">
         <v>372461.668130185</v>
       </c>
-      <c r="BD24" t="n">
+      <c r="BF24" t="n">
         <v>162.951979806956</v>
       </c>
-      <c r="BE24" t="n">
+      <c r="BG24" t="n">
         <v>782169.5030733886</v>
       </c>
-      <c r="BF24" t="n">
+      <c r="BH24" t="n">
         <v>-58.44802019304404</v>
       </c>
-      <c r="BG24" t="n">
+      <c r="BI24" t="n">
         <v>-280550.4969266114</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>E94H6</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="D25" t="n">
         <v>1400</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>1399.957</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>135.548</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>51.639</v>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="n">
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6.xlsx</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>809</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>2.1</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>24600</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>63.83065512978986</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>134.0443757725587</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>0.3841339430067745</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>38.41339430067745</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>29.065</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>34.07385697538101</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>183.9988276670574</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>42.29588521748337</v>
       </c>
-      <c r="U25" t="n">
+      <c r="W25" t="n">
         <v>142.0559</v>
       </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
         <v>-49.95445189449873</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>-27.14933161687878</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>22.574</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
         <v>29.75679815440886</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AB25" t="n">
         <v>-3.882490916805914</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>3150</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>34</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="n">
         <v>107100</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AF25" t="n">
         <v>183.6</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AG25" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AH25" t="n">
         <v>63.69229864352884</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>200630.7407271159</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AJ25" t="n">
         <v>133.7538271514106</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AK25" t="n">
         <v>421324.5555269433</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AL25" t="n">
         <v>-49.84617284858945</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AM25" t="n">
         <v>-157015.4444730568</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AN25" t="n">
         <v>1675</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AO25" t="n">
         <v>12.1</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AP25" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AQ25" t="n">
         <v>65.34</v>
       </c>
-      <c r="AP25" t="n">
+      <c r="AR25" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AS25" t="n">
         <v>22.66696510549114</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AT25" t="n">
         <v>37967.16655169766</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AU25" t="n">
         <v>47.60062672153141</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AV25" t="n">
         <v>79731.0497585651</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AW25" t="n">
         <v>-17.7393732784686</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AX25" t="n">
         <v>-29713.4502414349</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AY25" t="n">
         <v>4800</v>
       </c>
-      <c r="AX25" t="n">
+      <c r="AZ25" t="n">
         <v>41</v>
       </c>
-      <c r="AY25" t="n">
+      <c r="BA25" t="n">
         <v>196800</v>
       </c>
-      <c r="AZ25" t="n">
+      <c r="BB25" t="n">
         <v>221.4</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BC25" t="n">
         <v>1062720</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BD25" t="n">
         <v>76.80541895249065</v>
       </c>
-      <c r="BC25" t="n">
+      <c r="BE25" t="n">
         <v>368666.0109719551</v>
       </c>
-      <c r="BD25" t="n">
+      <c r="BF25" t="n">
         <v>161.2913798002304</v>
       </c>
-      <c r="BE25" t="n">
+      <c r="BG25" t="n">
         <v>774198.6230411058</v>
       </c>
-      <c r="BF25" t="n">
+      <c r="BH25" t="n">
         <v>-60.10862019976963</v>
       </c>
-      <c r="BG25" t="n">
+      <c r="BI25" t="n">
         <v>-288521.3769588942</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>E94H6</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="D26" t="n">
         <v>1500</v>
       </c>
-      <c r="C26" t="n">
+      <c r="E26" t="n">
         <v>1499.988</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>153.6389</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>58.213</v>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6.xlsx</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>809</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>2.1</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>24600</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>71.95673671199012</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>151.1091470951793</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.3862323100237857</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>38.62323100237857</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>32.921</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>38.59437280187574</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>208.409613130129</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>41.6651634565732</v>
       </c>
-      <c r="U26" t="n">
+      <c r="W26" t="n">
         <v>158.5028</v>
       </c>
-      <c r="V26" t="n">
+      <c r="X26" t="n">
         <v>-57.30046603494972</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Y26" t="n">
         <v>-27.49415690300805</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>25.292</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>33.36236391011438</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
         <v>-3.041932454194622</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>3150</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>34</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>107100</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>183.6</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AG26" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>63.39082282194155</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
         <v>199681.0918891159</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AJ26" t="n">
         <v>133.1207279260773</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AK26" t="n">
         <v>419330.2929671434</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AL26" t="n">
         <v>-50.47927207392277</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AM26" t="n">
         <v>-159009.7070328568</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AN26" t="n">
         <v>1675</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AO26" t="n">
         <v>12.1</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AP26" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AO26" t="n">
+      <c r="AQ26" t="n">
         <v>65.34</v>
       </c>
-      <c r="AP26" t="n">
+      <c r="AR26" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AS26" t="n">
         <v>22.55967518074978</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AT26" t="n">
         <v>37787.45592775589</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AU26" t="n">
         <v>47.37531787957455</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="AV26" t="n">
         <v>79353.65744828737</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AW26" t="n">
         <v>-17.96468212042546</v>
       </c>
-      <c r="AV26" t="n">
+      <c r="AX26" t="n">
         <v>-30090.84255171263</v>
       </c>
-      <c r="AW26" t="n">
+      <c r="AY26" t="n">
         <v>4800</v>
       </c>
-      <c r="AX26" t="n">
+      <c r="AZ26" t="n">
         <v>41</v>
       </c>
-      <c r="AY26" t="n">
+      <c r="BA26" t="n">
         <v>196800</v>
       </c>
-      <c r="AZ26" t="n">
+      <c r="BB26" t="n">
         <v>221.4</v>
       </c>
-      <c r="BA26" t="n">
+      <c r="BC26" t="n">
         <v>1062720</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BD26" t="n">
         <v>76.44187457940009</v>
       </c>
-      <c r="BC26" t="n">
+      <c r="BE26" t="n">
         <v>366920.9979811204</v>
       </c>
-      <c r="BD26" t="n">
+      <c r="BF26" t="n">
         <v>160.5279366167402</v>
       </c>
-      <c r="BE26" t="n">
+      <c r="BG26" t="n">
         <v>770534.0957603529</v>
       </c>
-      <c r="BF26" t="n">
+      <c r="BH26" t="n">
         <v>-60.87206338325981</v>
       </c>
-      <c r="BG26" t="n">
+      <c r="BI26" t="n">
         <v>-292185.9042396471</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>E94H6</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="D27" t="n">
         <v>1600</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>1600.025</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>165.6302</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>62.66</v>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6.xlsx</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>809</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>2.1</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>24600</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>77.45364647713227</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>162.6526576019778</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.3868267771091372</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>38.68267771091372</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>34.72</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>40.70339976553341</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>219.7983587338804</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>41.8835186990429</v>
       </c>
-      <c r="U27" t="n">
+      <c r="W27" t="n">
         <v>168.0404</v>
       </c>
-      <c r="V27" t="n">
+      <c r="X27" t="n">
         <v>-57.14570113190265</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Y27" t="n">
         <v>-25.99914824709473</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>27.94</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>36.75024671159886</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AB27" t="n">
         <v>-3.200840988129173</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>3150</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>34</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
         <v>107100</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
         <v>183.6</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>64.69788753254004</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>203798.3457275011</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AJ27" t="n">
         <v>135.8655638183341</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AK27" t="n">
         <v>427976.5260277524</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AL27" t="n">
         <v>-47.73443618166593</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AM27" t="n">
         <v>-150363.4739722477</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AN27" t="n">
         <v>1675</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="AO27" t="n">
         <v>12.1</v>
       </c>
-      <c r="AN27" t="n">
+      <c r="AP27" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AO27" t="n">
+      <c r="AQ27" t="n">
         <v>65.34</v>
       </c>
-      <c r="AP27" t="n">
+      <c r="AR27" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AS27" t="n">
         <v>23.02483644540396</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AT27" t="n">
         <v>38566.60104605163</v>
       </c>
-      <c r="AS27" t="n">
+      <c r="AU27" t="n">
         <v>48.35215653534831</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AV27" t="n">
         <v>80989.86219670842</v>
       </c>
-      <c r="AU27" t="n">
+      <c r="AW27" t="n">
         <v>-16.9878434646517</v>
       </c>
-      <c r="AV27" t="n">
+      <c r="AX27" t="n">
         <v>-28454.63780329158</v>
       </c>
-      <c r="AW27" t="n">
+      <c r="AY27" t="n">
         <v>4800</v>
       </c>
-      <c r="AX27" t="n">
+      <c r="AZ27" t="n">
         <v>41</v>
       </c>
-      <c r="AY27" t="n">
+      <c r="BA27" t="n">
         <v>196800</v>
       </c>
-      <c r="AZ27" t="n">
+      <c r="BB27" t="n">
         <v>221.4</v>
       </c>
-      <c r="BA27" t="n">
+      <c r="BC27" t="n">
         <v>1062720</v>
       </c>
-      <c r="BB27" t="n">
+      <c r="BD27" t="n">
         <v>78.01804084806299</v>
       </c>
-      <c r="BC27" t="n">
+      <c r="BE27" t="n">
         <v>374486.5960707024</v>
       </c>
-      <c r="BD27" t="n">
+      <c r="BF27" t="n">
         <v>163.8378857809323</v>
       </c>
-      <c r="BE27" t="n">
+      <c r="BG27" t="n">
         <v>786421.851748475</v>
       </c>
-      <c r="BF27" t="n">
+      <c r="BH27" t="n">
         <v>-57.56211421906772</v>
       </c>
-      <c r="BG27" t="n">
+      <c r="BI27" t="n">
         <v>-276298.148251525</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>E94H6</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="D28" t="n">
         <v>1700</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>1699.985</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>174.2287</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>65.848</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="n">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6.xlsx</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>809</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>2.1</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>24600</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>81.39431396786156</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>170.9280593325093</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.3872081601085723</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>38.72081601085723</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>36.915</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>43.27667057444314</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>233.694021101993</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>41.93000031256837</v>
       </c>
-      <c r="U28" t="n">
+      <c r="W28" t="n">
         <v>178.8622</v>
       </c>
-      <c r="V28" t="n">
+      <c r="X28" t="n">
         <v>-62.76596176948371</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Y28" t="n">
         <v>-26.85818039909983</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Z28" t="n">
         <v>28.933</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
         <v>38.11764339341842</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
         <v>-3.209184301711147</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AC28" t="n">
         <v>3150</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
         <v>34</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>107100</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>183.6</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AH28" t="n">
         <v>63.94684799392986</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AI28" t="n">
         <v>201432.5711808791</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AJ28" t="n">
         <v>134.2883807872527</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AK28" t="n">
         <v>423008.3994798461</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AL28" t="n">
         <v>-49.3116192127473</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AM28" t="n">
         <v>-155331.6005201541</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AN28" t="n">
         <v>1675</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AO28" t="n">
         <v>12.1</v>
       </c>
-      <c r="AN28" t="n">
+      <c r="AP28" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AO28" t="n">
+      <c r="AQ28" t="n">
         <v>65.34</v>
       </c>
-      <c r="AP28" t="n">
+      <c r="AR28" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AS28" t="n">
         <v>22.75755472725151</v>
       </c>
-      <c r="AR28" t="n">
+      <c r="AT28" t="n">
         <v>38118.90416814628</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AU28" t="n">
         <v>47.79086492722817</v>
       </c>
-      <c r="AT28" t="n">
+      <c r="AV28" t="n">
         <v>80049.69875310718</v>
       </c>
-      <c r="AU28" t="n">
+      <c r="AW28" t="n">
         <v>-17.54913507277183</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AX28" t="n">
         <v>-29394.80124689282</v>
       </c>
-      <c r="AW28" t="n">
+      <c r="AY28" t="n">
         <v>4800</v>
       </c>
-      <c r="AX28" t="n">
+      <c r="AZ28" t="n">
         <v>41</v>
       </c>
-      <c r="AY28" t="n">
+      <c r="BA28" t="n">
         <v>196800</v>
       </c>
-      <c r="AZ28" t="n">
+      <c r="BB28" t="n">
         <v>221.4</v>
       </c>
-      <c r="BA28" t="n">
+      <c r="BC28" t="n">
         <v>1062720</v>
       </c>
-      <c r="BB28" t="n">
+      <c r="BD28" t="n">
         <v>77.1123755220919</v>
       </c>
-      <c r="BC28" t="n">
+      <c r="BE28" t="n">
         <v>370139.4025060411</v>
       </c>
-      <c r="BD28" t="n">
+      <c r="BF28" t="n">
         <v>161.935988596393</v>
       </c>
-      <c r="BE28" t="n">
+      <c r="BG28" t="n">
         <v>777292.7452626863</v>
       </c>
-      <c r="BF28" t="n">
+      <c r="BH28" t="n">
         <v>-59.46401140360703</v>
       </c>
-      <c r="BG28" t="n">
+      <c r="BI28" t="n">
         <v>-285427.2547373137</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>E94H6</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="D29" t="n">
         <v>1800</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>1800.025</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>176.8714</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>66.93300000000001</v>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="n">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6.xlsx</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>809</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>2.1</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>24600</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>82.73547589616811</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>173.744499381953</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.3867093886751695</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>38.67093886751694</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>39.393</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>46.18171160609613</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>249.3812426729191</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>41.62516915344194</v>
       </c>
-      <c r="U29" t="n">
+      <c r="W29" t="n">
         <v>189.4811</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>-75.63674329096608</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
         <v>-30.32976437212198</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>27.54000000000001</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
         <v>36.55376429007198</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
         <v>-2.954230285924993</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>3150</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>34</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
         <v>107100</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>183.6</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>60.91169172037336</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>191871.8289191761</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AJ29" t="n">
         <v>127.9145526127841</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AK29" t="n">
         <v>402930.8407302698</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AL29" t="n">
         <v>-55.68544738721596</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AM29" t="n">
         <v>-175409.1592697303</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AN29" t="n">
         <v>1675</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AO29" t="n">
         <v>12.1</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AP29" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AO29" t="n">
+      <c r="AQ29" t="n">
         <v>65.34</v>
       </c>
-      <c r="AP29" t="n">
+      <c r="AR29" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AS29" t="n">
         <v>21.67739617107405</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AT29" t="n">
         <v>36309.63858654903</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AU29" t="n">
         <v>45.5225319592555</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AV29" t="n">
         <v>76250.24103175297</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AW29" t="n">
         <v>-19.8174680407445</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AX29" t="n">
         <v>-33194.25896824703</v>
       </c>
-      <c r="AW29" t="n">
+      <c r="AY29" t="n">
         <v>4800</v>
       </c>
-      <c r="AX29" t="n">
+      <c r="AZ29" t="n">
         <v>41</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="BA29" t="n">
         <v>196800</v>
       </c>
-      <c r="AZ29" t="n">
+      <c r="BB29" t="n">
         <v>221.4</v>
       </c>
-      <c r="BA29" t="n">
+      <c r="BC29" t="n">
         <v>1062720</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BD29" t="n">
         <v>73.4523341333914</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BE29" t="n">
         <v>352571.2038402787</v>
       </c>
-      <c r="BD29" t="n">
+      <c r="BF29" t="n">
         <v>154.249901680122</v>
       </c>
-      <c r="BE29" t="n">
+      <c r="BG29" t="n">
         <v>740399.5280645854</v>
       </c>
-      <c r="BF29" t="n">
+      <c r="BH29" t="n">
         <v>-67.15009831987805</v>
       </c>
-      <c r="BG29" t="n">
+      <c r="BI29" t="n">
         <v>-322320.4719354146</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>E94H6</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="D30" t="n">
         <v>1900</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>1899.959</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>180.749</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>68.246</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="n">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6.xlsx</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>809</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>2.1</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>24600</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>84.3584672435105</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>177.1527812113721</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>0.387584227218177</v>
       </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
         <v>38.75842272181769</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>41.813</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>49.01875732708089</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>264.7012895662368</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>41.29962341487465</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>199.5484</v>
       </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
         <v>-87.54850835486477</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
         <v>-33.07445479329911</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Z30" t="n">
         <v>26.43299999999999</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>35.33970991642961</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AB30" t="n">
         <v>-2.54120069305695</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>3150</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>34</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AE30" t="n">
         <v>107100</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AF30" t="n">
         <v>183.6</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>58.51204809500135</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>184312.9514992542</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AJ30" t="n">
         <v>122.8753009995028</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AK30" t="n">
         <v>387057.1981484339</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AL30" t="n">
         <v>-60.72469900049718</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AM30" t="n">
         <v>-191282.8018515662</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AN30" t="n">
         <v>1675</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AO30" t="n">
         <v>12.1</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AP30" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AO30" t="n">
+      <c r="AQ30" t="n">
         <v>65.34</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AR30" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AS30" t="n">
         <v>20.82340535145636</v>
       </c>
-      <c r="AR30" t="n">
+      <c r="AT30" t="n">
         <v>34879.2039636894</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AU30" t="n">
         <v>43.72915123805836</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="AV30" t="n">
         <v>73246.32832374776</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AW30" t="n">
         <v>-21.61084876194164</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AX30" t="n">
         <v>-36198.17167625224</v>
       </c>
-      <c r="AW30" t="n">
+      <c r="AY30" t="n">
         <v>4800</v>
       </c>
-      <c r="AX30" t="n">
+      <c r="AZ30" t="n">
         <v>41</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="BA30" t="n">
         <v>196800</v>
       </c>
-      <c r="AZ30" t="n">
+      <c r="BB30" t="n">
         <v>221.4</v>
       </c>
-      <c r="BA30" t="n">
+      <c r="BC30" t="n">
         <v>1062720</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BD30" t="n">
         <v>70.55864623220751</v>
       </c>
-      <c r="BC30" t="n">
+      <c r="BE30" t="n">
         <v>338681.501914596</v>
       </c>
-      <c r="BD30" t="n">
+      <c r="BF30" t="n">
         <v>148.1731570876358</v>
       </c>
-      <c r="BE30" t="n">
+      <c r="BG30" t="n">
         <v>711231.1540206516</v>
       </c>
-      <c r="BF30" t="n">
+      <c r="BH30" t="n">
         <v>-73.22684291236425</v>
       </c>
-      <c r="BG30" t="n">
+      <c r="BI30" t="n">
         <v>-351488.8459793484</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>E94H6</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="D31" t="n">
         <v>2000</v>
       </c>
-      <c r="C31" t="n">
+      <c r="E31" t="n">
         <v>1999.957</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>180.2096</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>67.595</v>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="n">
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6.xlsx</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>809</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>2.1</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>24600</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>83.55377008652657</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>175.4629171817058</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>0.3901492208797375</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>39.01492208797374</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>43.791</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>51.33763188745603</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>277.2232121922626</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>40.69333266582701</v>
       </c>
-      <c r="U31" t="n">
+      <c r="W31" t="n">
         <v>205.9202</v>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" t="n">
         <v>-101.7602950105568</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>-36.70698936277493</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Z31" t="n">
         <v>23.804</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
         <v>32.21613819907054</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AB31" t="n">
         <v>-1.678410577853271</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>3150</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>34</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>107100</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>183.6</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AH31" t="n">
         <v>55.33617501425964</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>174308.9512949178</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AJ31" t="n">
         <v>116.2059675299452</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AK31" t="n">
         <v>366048.7977193275</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AL31" t="n">
         <v>-67.39403247005478</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AM31" t="n">
         <v>-212291.2022806726</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AN31" t="n">
         <v>1675</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AO31" t="n">
         <v>12.1</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AP31" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AO31" t="n">
+      <c r="AQ31" t="n">
         <v>65.34</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AR31" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AS31" t="n">
         <v>19.69316816683946</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AT31" t="n">
         <v>32986.05667945609</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AU31" t="n">
         <v>41.35565315036286</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AV31" t="n">
         <v>69270.7190268578</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AW31" t="n">
         <v>-23.98434684963714</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AX31" t="n">
         <v>-40173.7809731422</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="AY31" t="n">
         <v>4800</v>
       </c>
-      <c r="AX31" t="n">
+      <c r="AZ31" t="n">
         <v>41</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="BA31" t="n">
         <v>196800</v>
       </c>
-      <c r="AZ31" t="n">
+      <c r="BB31" t="n">
         <v>221.4</v>
       </c>
-      <c r="BA31" t="n">
+      <c r="BC31" t="n">
         <v>1062720</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BD31" t="n">
         <v>66.72891692896013</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BE31" t="n">
         <v>320298.8012590086</v>
       </c>
-      <c r="BD31" t="n">
+      <c r="BF31" t="n">
         <v>140.1307255508163</v>
       </c>
-      <c r="BE31" t="n">
+      <c r="BG31" t="n">
         <v>672627.4826439183</v>
       </c>
-      <c r="BF31" t="n">
+      <c r="BH31" t="n">
         <v>-81.26927444918371</v>
       </c>
-      <c r="BG31" t="n">
+      <c r="BI31" t="n">
         <v>-390092.5173560817</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>E94H6</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="D32" t="n">
         <v>2100</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>2099.989</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>176.3708</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>67.64</v>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="n">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6.xlsx</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>809</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>2.1</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>24600</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>83.60939431396787</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>175.5797280593325</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>0.3815842840864836</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>38.15842840864836</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>40.444</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>47.41383352872216</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>256.0347010550997</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>40.81284282921114</v>
       </c>
-      <c r="U32" t="n">
+      <c r="W32" t="n">
         <v>190.74</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>-80.45497299576715</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>-31.42346434456669</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>27.196</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>36.19556078524571</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
         <v>-2.65441442056278</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>3150</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>34</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AE32" t="n">
         <v>107100</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AF32" t="n">
         <v>183.6</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AH32" t="n">
         <v>59.95548545875027</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AI32" t="n">
         <v>188859.7791950633</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AJ32" t="n">
         <v>125.9065194633756</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AK32" t="n">
         <v>396605.5363096331</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AL32" t="n">
         <v>-57.69348053662445</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AM32" t="n">
         <v>-181734.4636903671</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AN32" t="n">
         <v>1675</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AO32" t="n">
         <v>12.1</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AP32" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AO32" t="n">
+      <c r="AQ32" t="n">
         <v>65.34</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AR32" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AS32" t="n">
         <v>21.33709923679054</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AT32" t="n">
         <v>35739.64122162414</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AU32" t="n">
         <v>44.80790839726013</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AV32" t="n">
         <v>75053.24656541072</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AW32" t="n">
         <v>-20.53209160273988</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AX32" t="n">
         <v>-34391.25343458928</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AY32" t="n">
         <v>4800</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AZ32" t="n">
         <v>41</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="BA32" t="n">
         <v>196800</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="BB32" t="n">
         <v>221.4</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BC32" t="n">
         <v>1062720</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BD32" t="n">
         <v>72.29926187672825</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BE32" t="n">
         <v>347036.4570082956</v>
       </c>
-      <c r="BD32" t="n">
+      <c r="BF32" t="n">
         <v>151.8284499411293</v>
       </c>
-      <c r="BE32" t="n">
+      <c r="BG32" t="n">
         <v>728776.5597174208</v>
       </c>
-      <c r="BF32" t="n">
+      <c r="BH32" t="n">
         <v>-69.57155005887066</v>
       </c>
-      <c r="BG32" t="n">
+      <c r="BI32" t="n">
         <v>-333943.4402825792</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>p241075_nef6_horsch_full_load_curve_sala01_puc_minas_d85b15__vs__p251122_nef67_175kw_mar_l_sn2040912_full_load_curve_rev24_e94h6</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>P241075_NEF6_HORSCH_FULL_LOAD_CURVE_SALA01_PUC MINAS_D85B15 vs P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>E94H6</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="D33" t="n">
         <v>2200</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>2199.984</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>176.4447</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>68.863</v>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="n">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>P251122_NEF67_175KW_MAR_l_SN2040912_Full_Load_Curve_rev24_E94H6.xlsx</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>809</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>2.1</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>24600</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>85.12113720642769</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>178.7543881334982</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.3749644309680975</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>37.49644309680975</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>39.015</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>45.73856975381008</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>246.9882766705745</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
         <v>39.95200070978618</v>
       </c>
-      <c r="U33" t="n">
+      <c r="W33" t="n">
         <v>180.1196</v>
       </c>
-      <c r="V33" t="n">
+      <c r="X33" t="n">
         <v>-68.2338885370763</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
         <v>-27.62636731462547</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
         <v>29.848</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
         <v>39.38256745261761</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AB33" t="n">
         <v>-2.455557612976428</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>3150</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>34</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
         <v>107100</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AF33" t="n">
         <v>183.6</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AG33" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AH33" t="n">
         <v>63.2752331477846</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AI33" t="n">
         <v>199316.9844155215</v>
       </c>
-      <c r="AH33" t="n">
+      <c r="AJ33" t="n">
         <v>132.8779896103477</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AK33" t="n">
         <v>418565.6672725952</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AL33" t="n">
         <v>-50.72201038965235</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AM33" t="n">
         <v>-159774.332727405</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AN33" t="n">
         <v>1675</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AO33" t="n">
         <v>12.1</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AP33" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AO33" t="n">
+      <c r="AQ33" t="n">
         <v>65.34</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AR33" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AS33" t="n">
         <v>22.51853885553511</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AT33" t="n">
         <v>37718.5525830213</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AU33" t="n">
         <v>47.28893159662373</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AV33" t="n">
         <v>79208.96042434474</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AW33" t="n">
         <v>-18.05106840337628</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AX33" t="n">
         <v>-30235.53957565526</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AY33" t="n">
         <v>4800</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="AZ33" t="n">
         <v>41</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="BA33" t="n">
         <v>196800</v>
       </c>
-      <c r="AZ33" t="n">
+      <c r="BB33" t="n">
         <v>221.4</v>
       </c>
-      <c r="BA33" t="n">
+      <c r="BC33" t="n">
         <v>1062720</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BD33" t="n">
         <v>76.30248703115201</v>
       </c>
-      <c r="BC33" t="n">
+      <c r="BE33" t="n">
         <v>366251.9377495297</v>
       </c>
-      <c r="BD33" t="n">
+      <c r="BF33" t="n">
         <v>160.2352227654192</v>
       </c>
-      <c r="BE33" t="n">
+      <c r="BG33" t="n">
         <v>769129.0692740122</v>
       </c>
-      <c r="BF33" t="n">
+      <c r="BH33" t="n">
         <v>-61.16477723458078</v>
       </c>
-      <c r="BG33" t="n">
+      <c r="BI33" t="n">
         <v>-293590.9307259878</v>
       </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>804</v>
+      </c>
+      <c r="E34" t="n">
+        <v>804.1636999999999</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.02908451</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>809</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O34" t="n">
+        <v>7.552533992583436</v>
+      </c>
+      <c r="P34" t="n">
+        <v>15.86032138442522</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.0006966071613907628</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.06966071613907628</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>900</v>
+      </c>
+      <c r="E35" t="n">
+        <v>899.965</v>
+      </c>
+      <c r="F35" t="n">
+        <v>153.0359</v>
+      </c>
+      <c r="G35" t="n">
+        <v>59.591</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>809</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O35" t="n">
+        <v>73.66007416563659</v>
+      </c>
+      <c r="P35" t="n">
+        <v>154.6861557478368</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.3758201332579686</v>
+      </c>
+      <c r="R35" t="n">
+        <v>37.58201332579686</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E36" t="n">
+        <v>999.899</v>
+      </c>
+      <c r="F36" t="n">
+        <v>182.1889</v>
+      </c>
+      <c r="G36" t="n">
+        <v>70.161</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>809</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O36" t="n">
+        <v>86.72558714462299</v>
+      </c>
+      <c r="P36" t="n">
+        <v>182.1237330037083</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.3800086977651749</v>
+      </c>
+      <c r="R36" t="n">
+        <v>38.00086977651749</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1100.059</v>
+      </c>
+      <c r="F37" t="n">
+        <v>236.6207</v>
+      </c>
+      <c r="G37" t="n">
+        <v>90.709</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>809</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O37" t="n">
+        <v>112.1248454882571</v>
+      </c>
+      <c r="P37" t="n">
+        <v>235.4621755253399</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.3817418283984513</v>
+      </c>
+      <c r="R37" t="n">
+        <v>38.17418283984513</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1199.668</v>
+      </c>
+      <c r="F38" t="n">
+        <v>261.7221</v>
+      </c>
+      <c r="G38" t="n">
+        <v>99.86499999999999</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>809</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O38" t="n">
+        <v>123.442521631644</v>
+      </c>
+      <c r="P38" t="n">
+        <v>259.2292954264524</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.3835257109292667</v>
+      </c>
+      <c r="R38" t="n">
+        <v>38.35257109292667</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr"/>
+      <c r="BI38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1300.024</v>
+      </c>
+      <c r="F39" t="n">
+        <v>280.1731</v>
+      </c>
+      <c r="G39" t="n">
+        <v>107.281</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>809</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O39" t="n">
+        <v>132.6093943139679</v>
+      </c>
+      <c r="P39" t="n">
+        <v>278.4797280593326</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.3821826927733208</v>
+      </c>
+      <c r="R39" t="n">
+        <v>38.21826927733208</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1400.075</v>
+      </c>
+      <c r="F40" t="n">
+        <v>300.4143</v>
+      </c>
+      <c r="G40" t="n">
+        <v>115.281</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>809</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O40" t="n">
+        <v>142.4981458590853</v>
+      </c>
+      <c r="P40" t="n">
+        <v>299.2461063040791</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.381355715969526</v>
+      </c>
+      <c r="R40" t="n">
+        <v>38.1355715969526</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr"/>
+      <c r="BA40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr"/>
+      <c r="BG40" t="inlineStr"/>
+      <c r="BH40" t="inlineStr"/>
+      <c r="BI40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1500.016</v>
+      </c>
+      <c r="F41" t="n">
+        <v>301.1655</v>
+      </c>
+      <c r="G41" t="n">
+        <v>116.68</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>809</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O41" t="n">
+        <v>144.2274412855377</v>
+      </c>
+      <c r="P41" t="n">
+        <v>302.8776266996292</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.3777254028111073</v>
+      </c>
+      <c r="R41" t="n">
+        <v>37.77254028111073</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr"/>
+      <c r="BH41" t="inlineStr"/>
+      <c r="BI41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1600.038</v>
+      </c>
+      <c r="F42" t="n">
+        <v>300.3554</v>
+      </c>
+      <c r="G42" t="n">
+        <v>117.308</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>809</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O42" t="n">
+        <v>145.0037082818294</v>
+      </c>
+      <c r="P42" t="n">
+        <v>304.5077873918418</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.3746926789348365</v>
+      </c>
+      <c r="R42" t="n">
+        <v>37.46926789348365</v>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="inlineStr"/>
+      <c r="BI42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1699.999</v>
+      </c>
+      <c r="F43" t="n">
+        <v>296.0968</v>
+      </c>
+      <c r="G43" t="n">
+        <v>117.119</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>809</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O43" t="n">
+        <v>144.770086526576</v>
+      </c>
+      <c r="P43" t="n">
+        <v>304.0171817058097</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.3699761697452185</v>
+      </c>
+      <c r="R43" t="n">
+        <v>36.99761697452185</v>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
+      <c r="BA43" t="inlineStr"/>
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="inlineStr"/>
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1799.979</v>
+      </c>
+      <c r="F44" t="n">
+        <v>291.8231</v>
+      </c>
+      <c r="G44" t="n">
+        <v>116.542</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>809</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O44" t="n">
+        <v>144.0568603213844</v>
+      </c>
+      <c r="P44" t="n">
+        <v>302.5194066749073</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.3664414503972399</v>
+      </c>
+      <c r="R44" t="n">
+        <v>36.64414503972399</v>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
+      <c r="BA44" t="inlineStr"/>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="inlineStr"/>
+      <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="inlineStr"/>
+      <c r="BG44" t="inlineStr"/>
+      <c r="BH44" t="inlineStr"/>
+      <c r="BI44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/out_FPT/lv_kpis_fpt.xlsx
+++ b/out_FPT/lv_kpis_fpt.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI44"/>
+  <dimension ref="A1:BM59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,225 +499,245 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>Custo_R_kWh</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>n_th</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>n_th_pct</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Diesel_Baseline_Consumo_kg_h</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Diesel_Baseline_Consumo_L_h</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Diesel_Baseline_Custo_R_h</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Diesel_Baseline_Custo_R_kWh</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>Diesel_Baseline_n_th_pct</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Diesel_Baseline_Power_kW</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_h</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_pct</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Economia_vs_Diesel_R_kWh</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Economia_vs_Diesel_R_kWh_pct</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Delta_Consumo_kg_h_vs_Diesel</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Delta_Consumo_L_h_vs_Diesel</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Delta_n_th_pct_vs_Diesel</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_Hours_Ano</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_Diesel_L_h</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_Diesel_L_ano</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_Diesel_Custo_R_h</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_Diesel_Custo_R_ano</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_E94H6_L_h</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_E94H6_L_ano</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_E94H6_Custo_R_h</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_E94H6_Custo_R_ano</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_Economia_R_h</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Scenario_Colheitadeira_Economia_R_ano</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_Hours_Ano</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_Diesel_L_h</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_Diesel_L_ano</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_Diesel_Custo_R_h</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_Diesel_Custo_R_ano</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_E94H6_L_h</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_E94H6_L_ano</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_E94H6_Custo_R_h</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_E94H6_Custo_R_ano</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_Economia_R_h</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>Scenario_Trator_Transbordo_Economia_R_ano</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_Hours_Ano</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_Diesel_L_h</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_Diesel_L_ano</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_Diesel_Custo_R_h</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_Diesel_Custo_R_ano</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_E94H6_L_h</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_E94H6_L_ano</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_E94H6_Custo_R_h</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_E94H6_Custo_R_ano</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_Economia_R_h</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>Scenario_Caminhao_Economia_R_ano</t>
         </is>
@@ -777,32 +797,32 @@
         <v>104.7017584994138</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.494237911495989</v>
+      </c>
+      <c r="R2" t="n">
         <v>0.3666351909472714</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>36.66351909472714</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>16.539</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>19.38921453692849</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>104.7017584994138</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
+        <v>1.494237911495989</v>
+      </c>
+      <c r="X2" t="n">
         <v>36.66351909472714</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>70.07034</v>
       </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
@@ -812,10 +832,18 @@
       <c r="AB2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
@@ -845,6 +873,10 @@
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -900,32 +932,32 @@
         <v>122.6996483001172</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.41795372973883</v>
+      </c>
+      <c r="R3" t="n">
         <v>0.3863597171840645</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>38.63597171840645</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>19.382</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>22.7221570926143</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>122.6996483001172</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
+        <v>1.41795372973883</v>
+      </c>
+      <c r="X3" t="n">
         <v>38.63597171840645</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>86.5329</v>
       </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
@@ -935,10 +967,18 @@
       <c r="AB3" t="n">
         <v>0</v>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
@@ -968,6 +1008,10 @@
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1023,32 +1067,32 @@
         <v>138.8806565064478</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.367320490870933</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.4006670021108439</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>40.06670021108439</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>21.938</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>25.71864009378664</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>138.8806565064478</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
+        <v>1.367320490870933</v>
+      </c>
+      <c r="X4" t="n">
         <v>40.06670021108439</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>101.5714</v>
       </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
@@ -1058,10 +1102,18 @@
       <c r="AB4" t="n">
         <v>0</v>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
@@ -1091,6 +1143,10 @@
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1146,32 +1202,32 @@
         <v>152.3268464243845</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.349845689446515</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.4058539478143002</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>40.58539478143002</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>24.062</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>28.20867526377491</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>152.3268464243845</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
+        <v>1.349845689446515</v>
+      </c>
+      <c r="X5" t="n">
         <v>40.58539478143002</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>112.8476</v>
       </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
@@ -1181,10 +1237,18 @@
       <c r="AB5" t="n">
         <v>0</v>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
@@ -1214,6 +1278,10 @@
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1269,32 +1337,32 @@
         <v>167.2227432590856</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.320738085230403</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.4147985191980082</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>41.47985191980082</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>26.415</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>30.96717467760844</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>167.2227432590856</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
+        <v>1.320738085230403</v>
+      </c>
+      <c r="X6" t="n">
         <v>41.47985191980082</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>126.6131</v>
       </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
@@ -1304,10 +1372,18 @@
       <c r="AB6" t="n">
         <v>0</v>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
@@ -1337,6 +1413,10 @@
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1392,32 +1472,32 @@
         <v>183.9988276670574</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.295256498794189</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.4229588521748336</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>42.29588521748337</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>29.065</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>34.07385697538101</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>183.9988276670574</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
+        <v>1.295256498794189</v>
+      </c>
+      <c r="X7" t="n">
         <v>42.29588521748337</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>142.0559</v>
       </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
@@ -1427,10 +1507,18 @@
       <c r="AB7" t="n">
         <v>0</v>
       </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
@@ -1460,6 +1548,10 @@
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1515,32 +1607,32 @@
         <v>208.409613130129</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.314863921205991</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.416651634565732</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>41.6651634565732</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>32.921</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>38.59437280187574</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>208.409613130129</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
+        <v>1.314863921205991</v>
+      </c>
+      <c r="X8" t="n">
         <v>41.6651634565732</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>158.5028</v>
       </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
@@ -1550,10 +1642,18 @@
       <c r="AB8" t="n">
         <v>0</v>
       </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
@@ -1583,6 +1683,10 @@
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1638,32 +1742,32 @@
         <v>219.7983587338804</v>
       </c>
       <c r="Q9" t="n">
+        <v>1.30800901886618</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.418835186990429</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>41.8835186990429</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>34.72</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>40.70339976553341</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>219.7983587338804</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
+        <v>1.30800901886618</v>
+      </c>
+      <c r="X9" t="n">
         <v>41.8835186990429</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>168.0404</v>
       </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
@@ -1673,10 +1777,18 @@
       <c r="AB9" t="n">
         <v>0</v>
       </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
@@ -1706,6 +1818,10 @@
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1761,32 +1877,32 @@
         <v>233.694021101993</v>
       </c>
       <c r="Q10" t="n">
+        <v>1.306559021984483</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.4193000031256838</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>41.93000031256837</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>36.915</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>43.27667057444314</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>233.694021101993</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
+        <v>1.306559021984483</v>
+      </c>
+      <c r="X10" t="n">
         <v>41.93000031256837</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>178.8622</v>
       </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
@@ -1796,10 +1912,18 @@
       <c r="AB10" t="n">
         <v>0</v>
       </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
@@ -1829,6 +1953,10 @@
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1884,32 +2012,32 @@
         <v>249.3812426729191</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.316127269014794</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.4162516915344194</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>41.62516915344194</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>39.393</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>46.18171160609613</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>249.3812426729191</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
+        <v>1.316127269014794</v>
+      </c>
+      <c r="X11" t="n">
         <v>41.62516915344194</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>189.4811</v>
       </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
@@ -1919,10 +2047,18 @@
       <c r="AB11" t="n">
         <v>0</v>
       </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
@@ -1952,6 +2088,10 @@
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2007,32 +2147,32 @@
         <v>264.7012895662368</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.326501688644143</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.4129962341487465</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>41.29962341487465</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>41.813</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>49.01875732708089</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>264.7012895662368</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
+        <v>1.326501688644143</v>
+      </c>
+      <c r="X12" t="n">
         <v>41.29962341487465</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>199.5484</v>
       </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
@@ -2042,10 +2182,18 @@
       <c r="AB12" t="n">
         <v>0</v>
       </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
@@ -2075,6 +2223,10 @@
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2130,32 +2282,32 @@
         <v>277.2232121922626</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.346265262913802</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.4069333266582701</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>40.69333266582701</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>43.791</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>51.33763188745603</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>277.2232121922626</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
+        <v>1.346265262913802</v>
+      </c>
+      <c r="X13" t="n">
         <v>40.69333266582701</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Y13" t="n">
         <v>205.9202</v>
       </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
@@ -2165,10 +2317,18 @@
       <c r="AB13" t="n">
         <v>0</v>
       </c>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
@@ -2198,6 +2358,10 @@
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2253,32 +2417,32 @@
         <v>256.0347010550997</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.342323063096884</v>
+      </c>
+      <c r="R14" t="n">
         <v>0.4081284282921114</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>40.81284282921114</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>40.444</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>47.41383352872216</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>256.0347010550997</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
+        <v>1.342323063096884</v>
+      </c>
+      <c r="X14" t="n">
         <v>40.81284282921114</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>190.74</v>
       </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
@@ -2288,10 +2452,18 @@
       <c r="AB14" t="n">
         <v>0</v>
       </c>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
@@ -2321,6 +2493,10 @@
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2376,32 +2552,32 @@
         <v>246.9882766705745</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.371245975843687</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.3995200070978618</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>39.95200070978618</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>39.015</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>45.73856975381008</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>246.9882766705745</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
+        <v>1.371245975843687</v>
+      </c>
+      <c r="X15" t="n">
         <v>39.95200070978618</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>180.1196</v>
       </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
@@ -2411,10 +2587,18 @@
       <c r="AB15" t="n">
         <v>0</v>
       </c>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr"/>
@@ -2444,6 +2628,10 @@
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2499,32 +2687,32 @@
         <v>246.7667057444314</v>
       </c>
       <c r="Q16" t="n">
+        <v>1.411075957605007</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.3882428858980937</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>38.82428858980938</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>38.98</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>45.69753810082063</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>246.7667057444314</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
+        <v>1.411075957605007</v>
+      </c>
+      <c r="X16" t="n">
         <v>38.82428858980938</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>174.8784</v>
       </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
@@ -2534,10 +2722,18 @@
       <c r="AB16" t="n">
         <v>0</v>
       </c>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
@@ -2567,6 +2763,10 @@
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2622,32 +2822,32 @@
         <v>245.7854630715123</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.433586897661111</v>
+      </c>
+      <c r="R17" t="n">
         <v>0.3821464906632324</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>38.21464906632324</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>38.825</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>45.5158264947245</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>245.7854630715123</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
+        <v>1.433586897661111</v>
+      </c>
+      <c r="X17" t="n">
         <v>38.21464906632324</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Y17" t="n">
         <v>171.4479</v>
       </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
@@ -2657,10 +2857,18 @@
       <c r="AB17" t="n">
         <v>0</v>
       </c>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
@@ -2690,6 +2898,10 @@
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2745,32 +2957,32 @@
         <v>256.7120750293083</v>
       </c>
       <c r="Q18" t="n">
+        <v>1.515867886720384</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.361403659778854</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>36.14036597788539</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>40.551</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>47.53927315357561</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>256.7120750293083</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
+        <v>1.515867886720384</v>
+      </c>
+      <c r="X18" t="n">
         <v>36.14036597788539</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>169.3499</v>
       </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
@@ -2780,10 +2992,18 @@
       <c r="AB18" t="n">
         <v>0</v>
       </c>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
@@ -2813,6 +3033,10 @@
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2868,32 +3092,32 @@
         <v>167.9950762016413</v>
       </c>
       <c r="Q19" t="n">
+        <v>1.722415186012362</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.3180651253257426</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>31.80651253257426</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>26.537</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>31.11019929660024</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>167.9950762016413</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
+        <v>1.722415186012362</v>
+      </c>
+      <c r="X19" t="n">
         <v>31.80651253257426</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>97.5346</v>
       </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
@@ -2903,10 +3127,18 @@
       <c r="AB19" t="n">
         <v>0</v>
       </c>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
@@ -2936,6 +3168,10 @@
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2991,12 +3227,14 @@
         <v>79.88566131025958</v>
       </c>
       <c r="Q20" t="n">
+        <v>1.14863637580954</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.3307163004497632</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>33.07163004497632</v>
       </c>
-      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -3039,6 +3277,10 @@
       <c r="BG20" t="inlineStr"/>
       <c r="BH20" t="inlineStr"/>
       <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3094,12 +3336,14 @@
         <v>92.88541409147095</v>
       </c>
       <c r="Q21" t="n">
+        <v>1.021421484355952</v>
+      </c>
+      <c r="R21" t="n">
         <v>0.371905994330323</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>37.1905994330323</v>
       </c>
-      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
@@ -3142,6 +3386,10 @@
       <c r="BG21" t="inlineStr"/>
       <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3197,138 +3445,150 @@
         <v>105.8929542645241</v>
       </c>
       <c r="Q22" t="n">
+        <v>1.053242035652716</v>
+      </c>
+      <c r="R22" t="n">
         <v>0.3606699694000912</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>36.06699694000912</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>21.938</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>25.71864009378664</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>138.8806565064478</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
+        <v>1.367320490870933</v>
+      </c>
+      <c r="X22" t="n">
         <v>40.06670021108439</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>101.5714</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>-32.98770224192374</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>-23.75255350293668</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
+        <v>-0.3140784552182163</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-22.97036117831891</v>
+      </c>
+      <c r="AD22" t="n">
         <v>18.856</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AE22" t="n">
         <v>24.70657622265341</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AF22" t="n">
         <v>-3.999703271075269</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AG22" t="n">
         <v>3150</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AH22" t="n">
         <v>34</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AI22" t="n">
         <v>107100</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AJ22" t="n">
         <v>183.6</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AK22" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AL22" t="n">
         <v>66.6620532231468</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AM22" t="n">
         <v>209985.4676529124</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AN22" t="n">
         <v>139.9903117686083</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AO22" t="n">
         <v>440969.4820711161</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AP22" t="n">
         <v>-43.60968823139174</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AQ22" t="n">
         <v>-137370.517928884</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AR22" t="n">
         <v>1675</v>
       </c>
-      <c r="AO22" t="n">
+      <c r="AS22" t="n">
         <v>12.1</v>
       </c>
-      <c r="AP22" t="n">
+      <c r="AT22" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AU22" t="n">
         <v>65.34</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="AV22" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AW22" t="n">
         <v>23.72384835294342</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AX22" t="n">
         <v>39737.44599118023</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AY22" t="n">
         <v>49.82008154118117</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AZ22" t="n">
         <v>83448.63658147847</v>
       </c>
-      <c r="AW22" t="n">
+      <c r="BA22" t="n">
         <v>-15.51991845881883</v>
       </c>
-      <c r="AX22" t="n">
+      <c r="BB22" t="n">
         <v>-25995.86341852153</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="BC22" t="n">
         <v>4800</v>
       </c>
-      <c r="AZ22" t="n">
+      <c r="BD22" t="n">
         <v>41</v>
       </c>
-      <c r="BA22" t="n">
+      <c r="BE22" t="n">
         <v>196800</v>
       </c>
-      <c r="BB22" t="n">
+      <c r="BF22" t="n">
         <v>221.4</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BG22" t="n">
         <v>1062720</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BH22" t="n">
         <v>80.38659359261818</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BI22" t="n">
         <v>385855.6492445673</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BJ22" t="n">
         <v>168.8118465444982</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BK22" t="n">
         <v>810296.8634135913</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BL22" t="n">
         <v>-52.58815345550181</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BM22" t="n">
         <v>-252423.1365864087</v>
       </c>
     </row>
@@ -3386,138 +3646,150 @@
         <v>114.0982694684796</v>
       </c>
       <c r="Q23" t="n">
+        <v>1.032110516818226</v>
+      </c>
+      <c r="R23" t="n">
         <v>0.3680543571446407</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>36.80543571446407</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>24.062</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>28.20867526377491</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>152.3268464243845</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
+        <v>1.349845689446515</v>
+      </c>
+      <c r="X23" t="n">
         <v>40.58539478143002</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Y23" t="n">
         <v>112.8476</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>-38.22857695590493</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>-25.09641461978385</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
+        <v>-0.3177351726282893</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-23.53862927536348</v>
+      </c>
+      <c r="AD23" t="n">
         <v>19.893</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AE23" t="n">
         <v>26.12383400692967</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AF23" t="n">
         <v>-3.779959066965944</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AG23" t="n">
         <v>3150</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AH23" t="n">
         <v>34</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AI23" t="n">
         <v>107100</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AJ23" t="n">
         <v>183.6</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AK23" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AL23" t="n">
         <v>65.48713464670327</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AM23" t="n">
         <v>206284.4741371153</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AN23" t="n">
         <v>137.5229827580769</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AO23" t="n">
         <v>433197.3956879421</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AP23" t="n">
         <v>-46.07701724192316</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AQ23" t="n">
         <v>-145142.604312058</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AR23" t="n">
         <v>1675</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AS23" t="n">
         <v>12.1</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AT23" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AU23" t="n">
         <v>65.34</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AV23" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AW23" t="n">
         <v>23.3057155654444</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AX23" t="n">
         <v>39037.07357211937</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AY23" t="n">
         <v>48.94200268743324</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AZ23" t="n">
         <v>81977.85450145067</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="BA23" t="n">
         <v>-16.39799731256677</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="BB23" t="n">
         <v>-27466.64549854933</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="BC23" t="n">
         <v>4800</v>
       </c>
-      <c r="AZ23" t="n">
+      <c r="BD23" t="n">
         <v>41</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BE23" t="n">
         <v>196800</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BF23" t="n">
         <v>221.4</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BG23" t="n">
         <v>1062720</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BH23" t="n">
         <v>78.96978001514218</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BI23" t="n">
         <v>379054.9440726825</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BJ23" t="n">
         <v>165.8365380317986</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BK23" t="n">
         <v>796015.3825526332</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BL23" t="n">
         <v>-55.56346196820144</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BM23" t="n">
         <v>-266704.6174473668</v>
       </c>
     </row>
@@ -3575,138 +3847,150 @@
         <v>123.0771322620519</v>
       </c>
       <c r="Q24" t="n">
+        <v>1.005068185535696</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.3779572154771618</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>37.79572154771618</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>26.415</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>30.96717467760844</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>167.2227432590856</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
+        <v>1.320738085230403</v>
+      </c>
+      <c r="X24" t="n">
         <v>41.47985191980082</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Y24" t="n">
         <v>126.6131</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Z24" t="n">
         <v>-44.14561099703366</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>-26.39928644672269</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
+        <v>-0.3156698996947078</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>-23.90102195316334</v>
+      </c>
+      <c r="AD24" t="n">
         <v>20.999</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AE24" t="n">
         <v>27.64098354241628</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AF24" t="n">
         <v>-3.684130372084645</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AG24" t="n">
         <v>3150</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AH24" t="n">
         <v>34</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AI24" t="n">
         <v>107100</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AJ24" t="n">
         <v>183.6</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AK24" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AL24" t="n">
         <v>64.34805242086532</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AM24" t="n">
         <v>202696.3651257257</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AN24" t="n">
         <v>135.1309100838172</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AO24" t="n">
         <v>425662.366764024</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AP24" t="n">
         <v>-48.46908991618287</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AQ24" t="n">
         <v>-152677.6332359761</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AR24" t="n">
         <v>1675</v>
       </c>
-      <c r="AO24" t="n">
+      <c r="AS24" t="n">
         <v>12.1</v>
       </c>
-      <c r="AP24" t="n">
+      <c r="AT24" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AU24" t="n">
         <v>65.34</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AV24" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AW24" t="n">
         <v>22.90033630271971</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="AX24" t="n">
         <v>38358.06330705552</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AY24" t="n">
         <v>48.09070623571139</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AZ24" t="n">
         <v>80551.93294481658</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="BA24" t="n">
         <v>-17.24929376428861</v>
       </c>
-      <c r="AX24" t="n">
+      <c r="BB24" t="n">
         <v>-28892.56705518342</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="BC24" t="n">
         <v>4800</v>
       </c>
-      <c r="AZ24" t="n">
+      <c r="BD24" t="n">
         <v>41</v>
       </c>
-      <c r="BA24" t="n">
+      <c r="BE24" t="n">
         <v>196800</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BF24" t="n">
         <v>221.4</v>
       </c>
-      <c r="BC24" t="n">
+      <c r="BG24" t="n">
         <v>1062720</v>
       </c>
-      <c r="BD24" t="n">
+      <c r="BH24" t="n">
         <v>77.59618086045522</v>
       </c>
-      <c r="BE24" t="n">
+      <c r="BI24" t="n">
         <v>372461.668130185</v>
       </c>
-      <c r="BF24" t="n">
+      <c r="BJ24" t="n">
         <v>162.951979806956</v>
       </c>
-      <c r="BG24" t="n">
+      <c r="BK24" t="n">
         <v>782169.5030733886</v>
       </c>
-      <c r="BH24" t="n">
+      <c r="BL24" t="n">
         <v>-58.44802019304404</v>
       </c>
-      <c r="BI24" t="n">
+      <c r="BM24" t="n">
         <v>-280550.4969266114</v>
       </c>
     </row>
@@ -3764,138 +4048,150 @@
         <v>134.0443757725587</v>
       </c>
       <c r="Q25" t="n">
+        <v>0.9889070718310762</v>
+      </c>
+      <c r="R25" t="n">
         <v>0.3841339430067745</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>38.41339430067745</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>29.065</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>34.07385697538101</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>183.9988276670574</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
+        <v>1.295256498794189</v>
+      </c>
+      <c r="X25" t="n">
         <v>42.29588521748337</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>142.0559</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>-49.95445189449873</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
         <v>-27.14933161687878</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AB25" t="n">
+        <v>-0.3063494269631128</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>-23.65164175962884</v>
+      </c>
+      <c r="AD25" t="n">
         <v>22.574</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AE25" t="n">
         <v>29.75679815440886</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AF25" t="n">
         <v>-3.882490916805914</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AG25" t="n">
         <v>3150</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AH25" t="n">
         <v>34</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AI25" t="n">
         <v>107100</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AJ25" t="n">
         <v>183.6</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AK25" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AL25" t="n">
         <v>63.69229864352884</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AM25" t="n">
         <v>200630.7407271159</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AN25" t="n">
         <v>133.7538271514106</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AO25" t="n">
         <v>421324.5555269433</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AP25" t="n">
         <v>-49.84617284858945</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AQ25" t="n">
         <v>-157015.4444730568</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AR25" t="n">
         <v>1675</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AS25" t="n">
         <v>12.1</v>
       </c>
-      <c r="AP25" t="n">
+      <c r="AT25" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AU25" t="n">
         <v>65.34</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AV25" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AW25" t="n">
         <v>22.66696510549114</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AX25" t="n">
         <v>37967.16655169766</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AY25" t="n">
         <v>47.60062672153141</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AZ25" t="n">
         <v>79731.0497585651</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="BA25" t="n">
         <v>-17.7393732784686</v>
       </c>
-      <c r="AX25" t="n">
+      <c r="BB25" t="n">
         <v>-29713.4502414349</v>
       </c>
-      <c r="AY25" t="n">
+      <c r="BC25" t="n">
         <v>4800</v>
       </c>
-      <c r="AZ25" t="n">
+      <c r="BD25" t="n">
         <v>41</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BE25" t="n">
         <v>196800</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BF25" t="n">
         <v>221.4</v>
       </c>
-      <c r="BC25" t="n">
+      <c r="BG25" t="n">
         <v>1062720</v>
       </c>
-      <c r="BD25" t="n">
+      <c r="BH25" t="n">
         <v>76.80541895249065</v>
       </c>
-      <c r="BE25" t="n">
+      <c r="BI25" t="n">
         <v>368666.0109719551</v>
       </c>
-      <c r="BF25" t="n">
+      <c r="BJ25" t="n">
         <v>161.2913798002304</v>
       </c>
-      <c r="BG25" t="n">
+      <c r="BK25" t="n">
         <v>774198.6230411058</v>
       </c>
-      <c r="BH25" t="n">
+      <c r="BL25" t="n">
         <v>-60.10862019976963</v>
       </c>
-      <c r="BI25" t="n">
+      <c r="BM25" t="n">
         <v>-288521.3769588942</v>
       </c>
     </row>
@@ -3953,138 +4249,150 @@
         <v>151.1091470951793</v>
       </c>
       <c r="Q26" t="n">
+        <v>0.9835344245186554</v>
+      </c>
+      <c r="R26" t="n">
         <v>0.3862323100237857</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>38.62323100237857</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>32.921</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>38.59437280187574</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>208.409613130129</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
+        <v>1.314863921205991</v>
+      </c>
+      <c r="X26" t="n">
         <v>41.6651634565732</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Y26" t="n">
         <v>158.5028</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>-57.30046603494972</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>-27.49415690300805</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
+        <v>-0.3313294966873358</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-25.19876706202729</v>
+      </c>
+      <c r="AD26" t="n">
         <v>25.292</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AE26" t="n">
         <v>33.36236391011438</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AF26" t="n">
         <v>-3.041932454194622</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AG26" t="n">
         <v>3150</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AH26" t="n">
         <v>34</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AI26" t="n">
         <v>107100</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AJ26" t="n">
         <v>183.6</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AK26" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AL26" t="n">
         <v>63.39082282194155</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AM26" t="n">
         <v>199681.0918891159</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AN26" t="n">
         <v>133.1207279260773</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AO26" t="n">
         <v>419330.2929671434</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AP26" t="n">
         <v>-50.47927207392277</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AQ26" t="n">
         <v>-159009.7070328568</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AR26" t="n">
         <v>1675</v>
       </c>
-      <c r="AO26" t="n">
+      <c r="AS26" t="n">
         <v>12.1</v>
       </c>
-      <c r="AP26" t="n">
+      <c r="AT26" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AU26" t="n">
         <v>65.34</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AV26" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AW26" t="n">
         <v>22.55967518074978</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="AX26" t="n">
         <v>37787.45592775589</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AY26" t="n">
         <v>47.37531787957455</v>
       </c>
-      <c r="AV26" t="n">
+      <c r="AZ26" t="n">
         <v>79353.65744828737</v>
       </c>
-      <c r="AW26" t="n">
+      <c r="BA26" t="n">
         <v>-17.96468212042546</v>
       </c>
-      <c r="AX26" t="n">
+      <c r="BB26" t="n">
         <v>-30090.84255171263</v>
       </c>
-      <c r="AY26" t="n">
+      <c r="BC26" t="n">
         <v>4800</v>
       </c>
-      <c r="AZ26" t="n">
+      <c r="BD26" t="n">
         <v>41</v>
       </c>
-      <c r="BA26" t="n">
+      <c r="BE26" t="n">
         <v>196800</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BF26" t="n">
         <v>221.4</v>
       </c>
-      <c r="BC26" t="n">
+      <c r="BG26" t="n">
         <v>1062720</v>
       </c>
-      <c r="BD26" t="n">
+      <c r="BH26" t="n">
         <v>76.44187457940009</v>
       </c>
-      <c r="BE26" t="n">
+      <c r="BI26" t="n">
         <v>366920.9979811204</v>
       </c>
-      <c r="BF26" t="n">
+      <c r="BJ26" t="n">
         <v>160.5279366167402</v>
       </c>
-      <c r="BG26" t="n">
+      <c r="BK26" t="n">
         <v>770534.0957603529</v>
       </c>
-      <c r="BH26" t="n">
+      <c r="BL26" t="n">
         <v>-60.87206338325981</v>
       </c>
-      <c r="BI26" t="n">
+      <c r="BM26" t="n">
         <v>-292185.9042396471</v>
       </c>
     </row>
@@ -4142,138 +4450,150 @@
         <v>162.6526576019778</v>
       </c>
       <c r="Q27" t="n">
+        <v>0.9820229499329094</v>
+      </c>
+      <c r="R27" t="n">
         <v>0.3868267771091372</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>38.68267771091372</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>34.72</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>40.70339976553341</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>219.7983587338804</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
+        <v>1.30800901886618</v>
+      </c>
+      <c r="X27" t="n">
         <v>41.8835186990429</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Y27" t="n">
         <v>168.0404</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>-57.14570113190265</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>-25.99914824709473</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AB27" t="n">
+        <v>-0.3259860689332705</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>-24.92231049108856</v>
+      </c>
+      <c r="AD27" t="n">
         <v>27.94</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AE27" t="n">
         <v>36.75024671159886</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AF27" t="n">
         <v>-3.200840988129173</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AG27" t="n">
         <v>3150</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AH27" t="n">
         <v>34</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AI27" t="n">
         <v>107100</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AJ27" t="n">
         <v>183.6</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AK27" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AL27" t="n">
         <v>64.69788753254004</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AM27" t="n">
         <v>203798.3457275011</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AN27" t="n">
         <v>135.8655638183341</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AO27" t="n">
         <v>427976.5260277524</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AP27" t="n">
         <v>-47.73443618166593</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="AQ27" t="n">
         <v>-150363.4739722477</v>
       </c>
-      <c r="AN27" t="n">
+      <c r="AR27" t="n">
         <v>1675</v>
       </c>
-      <c r="AO27" t="n">
+      <c r="AS27" t="n">
         <v>12.1</v>
       </c>
-      <c r="AP27" t="n">
+      <c r="AT27" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AU27" t="n">
         <v>65.34</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AV27" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AS27" t="n">
+      <c r="AW27" t="n">
         <v>23.02483644540396</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AX27" t="n">
         <v>38566.60104605163</v>
       </c>
-      <c r="AU27" t="n">
+      <c r="AY27" t="n">
         <v>48.35215653534831</v>
       </c>
-      <c r="AV27" t="n">
+      <c r="AZ27" t="n">
         <v>80989.86219670842</v>
       </c>
-      <c r="AW27" t="n">
+      <c r="BA27" t="n">
         <v>-16.9878434646517</v>
       </c>
-      <c r="AX27" t="n">
+      <c r="BB27" t="n">
         <v>-28454.63780329158</v>
       </c>
-      <c r="AY27" t="n">
+      <c r="BC27" t="n">
         <v>4800</v>
       </c>
-      <c r="AZ27" t="n">
+      <c r="BD27" t="n">
         <v>41</v>
       </c>
-      <c r="BA27" t="n">
+      <c r="BE27" t="n">
         <v>196800</v>
       </c>
-      <c r="BB27" t="n">
+      <c r="BF27" t="n">
         <v>221.4</v>
       </c>
-      <c r="BC27" t="n">
+      <c r="BG27" t="n">
         <v>1062720</v>
       </c>
-      <c r="BD27" t="n">
+      <c r="BH27" t="n">
         <v>78.01804084806299</v>
       </c>
-      <c r="BE27" t="n">
+      <c r="BI27" t="n">
         <v>374486.5960707024</v>
       </c>
-      <c r="BF27" t="n">
+      <c r="BJ27" t="n">
         <v>163.8378857809323</v>
       </c>
-      <c r="BG27" t="n">
+      <c r="BK27" t="n">
         <v>786421.851748475</v>
       </c>
-      <c r="BH27" t="n">
+      <c r="BL27" t="n">
         <v>-57.56211421906772</v>
       </c>
-      <c r="BI27" t="n">
+      <c r="BM27" t="n">
         <v>-276298.148251525</v>
       </c>
     </row>
@@ -4331,138 +4651,150 @@
         <v>170.9280593325093</v>
       </c>
       <c r="Q28" t="n">
+        <v>0.9810557005390576</v>
+      </c>
+      <c r="R28" t="n">
         <v>0.3872081601085723</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>38.72081601085723</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>36.915</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>43.27667057444314</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>233.694021101993</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
+        <v>1.306559021984483</v>
+      </c>
+      <c r="X28" t="n">
         <v>41.93000031256837</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Y28" t="n">
         <v>178.8622</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Z28" t="n">
         <v>-62.76596176948371</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
         <v>-26.85818039909983</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
+        <v>-0.3255033214454254</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>-24.91302084088255</v>
+      </c>
+      <c r="AD28" t="n">
         <v>28.933</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AE28" t="n">
         <v>38.11764339341842</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AF28" t="n">
         <v>-3.209184301711147</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AG28" t="n">
         <v>3150</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AH28" t="n">
         <v>34</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AI28" t="n">
         <v>107100</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AJ28" t="n">
         <v>183.6</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AK28" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AL28" t="n">
         <v>63.94684799392986</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AM28" t="n">
         <v>201432.5711808791</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AN28" t="n">
         <v>134.2883807872527</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AO28" t="n">
         <v>423008.3994798461</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AP28" t="n">
         <v>-49.3116192127473</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AQ28" t="n">
         <v>-155331.6005201541</v>
       </c>
-      <c r="AN28" t="n">
+      <c r="AR28" t="n">
         <v>1675</v>
       </c>
-      <c r="AO28" t="n">
+      <c r="AS28" t="n">
         <v>12.1</v>
       </c>
-      <c r="AP28" t="n">
+      <c r="AT28" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AU28" t="n">
         <v>65.34</v>
       </c>
-      <c r="AR28" t="n">
+      <c r="AV28" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AW28" t="n">
         <v>22.75755472725151</v>
       </c>
-      <c r="AT28" t="n">
+      <c r="AX28" t="n">
         <v>38118.90416814628</v>
       </c>
-      <c r="AU28" t="n">
+      <c r="AY28" t="n">
         <v>47.79086492722817</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AZ28" t="n">
         <v>80049.69875310718</v>
       </c>
-      <c r="AW28" t="n">
+      <c r="BA28" t="n">
         <v>-17.54913507277183</v>
       </c>
-      <c r="AX28" t="n">
+      <c r="BB28" t="n">
         <v>-29394.80124689282</v>
       </c>
-      <c r="AY28" t="n">
+      <c r="BC28" t="n">
         <v>4800</v>
       </c>
-      <c r="AZ28" t="n">
+      <c r="BD28" t="n">
         <v>41</v>
       </c>
-      <c r="BA28" t="n">
+      <c r="BE28" t="n">
         <v>196800</v>
       </c>
-      <c r="BB28" t="n">
+      <c r="BF28" t="n">
         <v>221.4</v>
       </c>
-      <c r="BC28" t="n">
+      <c r="BG28" t="n">
         <v>1062720</v>
       </c>
-      <c r="BD28" t="n">
+      <c r="BH28" t="n">
         <v>77.1123755220919</v>
       </c>
-      <c r="BE28" t="n">
+      <c r="BI28" t="n">
         <v>370139.4025060411</v>
       </c>
-      <c r="BF28" t="n">
+      <c r="BJ28" t="n">
         <v>161.935988596393</v>
       </c>
-      <c r="BG28" t="n">
+      <c r="BK28" t="n">
         <v>777292.7452626863</v>
       </c>
-      <c r="BH28" t="n">
+      <c r="BL28" t="n">
         <v>-59.46401140360703</v>
       </c>
-      <c r="BI28" t="n">
+      <c r="BM28" t="n">
         <v>-285427.2547373137</v>
       </c>
     </row>
@@ -4520,138 +4852,150 @@
         <v>173.744499381953</v>
       </c>
       <c r="Q29" t="n">
+        <v>0.9823210501073268</v>
+      </c>
+      <c r="R29" t="n">
         <v>0.3867093886751695</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>38.67093886751694</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>39.393</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>46.18171160609613</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>249.3812426729191</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
+        <v>1.316127269014794</v>
+      </c>
+      <c r="X29" t="n">
         <v>41.62516915344194</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
         <v>189.4811</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>-75.63674329096608</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
         <v>-30.32976437212198</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
+        <v>-0.3338062189074674</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>-25.36276139596612</v>
+      </c>
+      <c r="AD29" t="n">
         <v>27.54000000000001</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AE29" t="n">
         <v>36.55376429007198</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AF29" t="n">
         <v>-2.954230285924993</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AG29" t="n">
         <v>3150</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AH29" t="n">
         <v>34</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AI29" t="n">
         <v>107100</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AJ29" t="n">
         <v>183.6</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AK29" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AL29" t="n">
         <v>60.91169172037336</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AM29" t="n">
         <v>191871.8289191761</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AN29" t="n">
         <v>127.9145526127841</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AO29" t="n">
         <v>402930.8407302698</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AP29" t="n">
         <v>-55.68544738721596</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AQ29" t="n">
         <v>-175409.1592697303</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AR29" t="n">
         <v>1675</v>
       </c>
-      <c r="AO29" t="n">
+      <c r="AS29" t="n">
         <v>12.1</v>
       </c>
-      <c r="AP29" t="n">
+      <c r="AT29" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AU29" t="n">
         <v>65.34</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AV29" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AW29" t="n">
         <v>21.67739617107405</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AX29" t="n">
         <v>36309.63858654903</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AY29" t="n">
         <v>45.5225319592555</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AZ29" t="n">
         <v>76250.24103175297</v>
       </c>
-      <c r="AW29" t="n">
+      <c r="BA29" t="n">
         <v>-19.8174680407445</v>
       </c>
-      <c r="AX29" t="n">
+      <c r="BB29" t="n">
         <v>-33194.25896824703</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="BC29" t="n">
         <v>4800</v>
       </c>
-      <c r="AZ29" t="n">
+      <c r="BD29" t="n">
         <v>41</v>
       </c>
-      <c r="BA29" t="n">
+      <c r="BE29" t="n">
         <v>196800</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BF29" t="n">
         <v>221.4</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BG29" t="n">
         <v>1062720</v>
       </c>
-      <c r="BD29" t="n">
+      <c r="BH29" t="n">
         <v>73.4523341333914</v>
       </c>
-      <c r="BE29" t="n">
+      <c r="BI29" t="n">
         <v>352571.2038402787</v>
       </c>
-      <c r="BF29" t="n">
+      <c r="BJ29" t="n">
         <v>154.249901680122</v>
       </c>
-      <c r="BG29" t="n">
+      <c r="BK29" t="n">
         <v>740399.5280645854</v>
       </c>
-      <c r="BH29" t="n">
+      <c r="BL29" t="n">
         <v>-67.15009831987805</v>
       </c>
-      <c r="BI29" t="n">
+      <c r="BM29" t="n">
         <v>-322320.4719354146</v>
       </c>
     </row>
@@ -4709,138 +5053,150 @@
         <v>177.1527812113721</v>
       </c>
       <c r="Q30" t="n">
+        <v>0.9801037970410462</v>
+      </c>
+      <c r="R30" t="n">
         <v>0.387584227218177</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>38.75842272181769</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>41.813</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>49.01875732708089</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>264.7012895662368</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
+        <v>1.326501688644143</v>
+      </c>
+      <c r="X30" t="n">
         <v>41.29962341487465</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
         <v>199.5484</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Z30" t="n">
         <v>-87.54850835486477</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>-33.07445479329911</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AB30" t="n">
+        <v>-0.3463978916030965</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>-26.11364120894262</v>
+      </c>
+      <c r="AD30" t="n">
         <v>26.43299999999999</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AE30" t="n">
         <v>35.33970991642961</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AF30" t="n">
         <v>-2.54120069305695</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AG30" t="n">
         <v>3150</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AH30" t="n">
         <v>34</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AI30" t="n">
         <v>107100</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AJ30" t="n">
         <v>183.6</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AK30" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AL30" t="n">
         <v>58.51204809500135</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AM30" t="n">
         <v>184312.9514992542</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AN30" t="n">
         <v>122.8753009995028</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AO30" t="n">
         <v>387057.1981484339</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AP30" t="n">
         <v>-60.72469900049718</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AQ30" t="n">
         <v>-191282.8018515662</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AR30" t="n">
         <v>1675</v>
       </c>
-      <c r="AO30" t="n">
+      <c r="AS30" t="n">
         <v>12.1</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AT30" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AU30" t="n">
         <v>65.34</v>
       </c>
-      <c r="AR30" t="n">
+      <c r="AV30" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AW30" t="n">
         <v>20.82340535145636</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="AX30" t="n">
         <v>34879.2039636894</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AY30" t="n">
         <v>43.72915123805836</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AZ30" t="n">
         <v>73246.32832374776</v>
       </c>
-      <c r="AW30" t="n">
+      <c r="BA30" t="n">
         <v>-21.61084876194164</v>
       </c>
-      <c r="AX30" t="n">
+      <c r="BB30" t="n">
         <v>-36198.17167625224</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="BC30" t="n">
         <v>4800</v>
       </c>
-      <c r="AZ30" t="n">
+      <c r="BD30" t="n">
         <v>41</v>
       </c>
-      <c r="BA30" t="n">
+      <c r="BE30" t="n">
         <v>196800</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BF30" t="n">
         <v>221.4</v>
       </c>
-      <c r="BC30" t="n">
+      <c r="BG30" t="n">
         <v>1062720</v>
       </c>
-      <c r="BD30" t="n">
+      <c r="BH30" t="n">
         <v>70.55864623220751</v>
       </c>
-      <c r="BE30" t="n">
+      <c r="BI30" t="n">
         <v>338681.501914596</v>
       </c>
-      <c r="BF30" t="n">
+      <c r="BJ30" t="n">
         <v>148.1731570876358</v>
       </c>
-      <c r="BG30" t="n">
+      <c r="BK30" t="n">
         <v>711231.1540206516</v>
       </c>
-      <c r="BH30" t="n">
+      <c r="BL30" t="n">
         <v>-73.22684291236425</v>
       </c>
-      <c r="BI30" t="n">
+      <c r="BM30" t="n">
         <v>-351488.8459793484</v>
       </c>
     </row>
@@ -4898,138 +5254,150 @@
         <v>175.4629171817058</v>
       </c>
       <c r="Q31" t="n">
+        <v>0.9736602111191957</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.3901492208797375</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>39.01492208797374</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>43.791</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>51.33763188745603</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>277.2232121922626</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
+        <v>1.346265262913802</v>
+      </c>
+      <c r="X31" t="n">
         <v>40.69333266582701</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>205.9202</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Z31" t="n">
         <v>-101.7602950105568</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
         <v>-36.70698936277493</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AB31" t="n">
+        <v>-0.372605051794606</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>-27.67694168890273</v>
+      </c>
+      <c r="AD31" t="n">
         <v>23.804</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AE31" t="n">
         <v>32.21613819907054</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AF31" t="n">
         <v>-1.678410577853271</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AG31" t="n">
         <v>3150</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AH31" t="n">
         <v>34</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AI31" t="n">
         <v>107100</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AJ31" t="n">
         <v>183.6</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AK31" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AL31" t="n">
         <v>55.33617501425964</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AM31" t="n">
         <v>174308.9512949178</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AN31" t="n">
         <v>116.2059675299452</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AO31" t="n">
         <v>366048.7977193275</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AP31" t="n">
         <v>-67.39403247005478</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AQ31" t="n">
         <v>-212291.2022806726</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AR31" t="n">
         <v>1675</v>
       </c>
-      <c r="AO31" t="n">
+      <c r="AS31" t="n">
         <v>12.1</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AT31" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AU31" t="n">
         <v>65.34</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AV31" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AW31" t="n">
         <v>19.69316816683946</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AX31" t="n">
         <v>32986.05667945609</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AY31" t="n">
         <v>41.35565315036286</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AZ31" t="n">
         <v>69270.7190268578</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="BA31" t="n">
         <v>-23.98434684963714</v>
       </c>
-      <c r="AX31" t="n">
+      <c r="BB31" t="n">
         <v>-40173.7809731422</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="BC31" t="n">
         <v>4800</v>
       </c>
-      <c r="AZ31" t="n">
+      <c r="BD31" t="n">
         <v>41</v>
       </c>
-      <c r="BA31" t="n">
+      <c r="BE31" t="n">
         <v>196800</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BF31" t="n">
         <v>221.4</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BG31" t="n">
         <v>1062720</v>
       </c>
-      <c r="BD31" t="n">
+      <c r="BH31" t="n">
         <v>66.72891692896013</v>
       </c>
-      <c r="BE31" t="n">
+      <c r="BI31" t="n">
         <v>320298.8012590086</v>
       </c>
-      <c r="BF31" t="n">
+      <c r="BJ31" t="n">
         <v>140.1307255508163</v>
       </c>
-      <c r="BG31" t="n">
+      <c r="BK31" t="n">
         <v>672627.4826439183</v>
       </c>
-      <c r="BH31" t="n">
+      <c r="BL31" t="n">
         <v>-81.26927444918371</v>
       </c>
-      <c r="BI31" t="n">
+      <c r="BM31" t="n">
         <v>-390092.5173560817</v>
       </c>
     </row>
@@ -5087,138 +5455,150 @@
         <v>175.5797280593325</v>
       </c>
       <c r="Q32" t="n">
+        <v>0.9955147227280963</v>
+      </c>
+      <c r="R32" t="n">
         <v>0.3815842840864836</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>38.15842840864836</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>40.444</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>47.41383352872216</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>256.0347010550997</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
+        <v>1.342323063096884</v>
+      </c>
+      <c r="X32" t="n">
         <v>40.81284282921114</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>190.74</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>-80.45497299576715</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>-31.42346434456669</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
+        <v>-0.3468083403687878</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>-25.83642864398556</v>
+      </c>
+      <c r="AD32" t="n">
         <v>27.196</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AE32" t="n">
         <v>36.19556078524571</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AF32" t="n">
         <v>-2.65441442056278</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AG32" t="n">
         <v>3150</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AH32" t="n">
         <v>34</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AI32" t="n">
         <v>107100</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AJ32" t="n">
         <v>183.6</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AK32" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AL32" t="n">
         <v>59.95548545875027</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AM32" t="n">
         <v>188859.7791950633</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AN32" t="n">
         <v>125.9065194633756</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AO32" t="n">
         <v>396605.5363096331</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AP32" t="n">
         <v>-57.69348053662445</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AQ32" t="n">
         <v>-181734.4636903671</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AR32" t="n">
         <v>1675</v>
       </c>
-      <c r="AO32" t="n">
+      <c r="AS32" t="n">
         <v>12.1</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AT32" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AU32" t="n">
         <v>65.34</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AV32" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AW32" t="n">
         <v>21.33709923679054</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AX32" t="n">
         <v>35739.64122162414</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AY32" t="n">
         <v>44.80790839726013</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AZ32" t="n">
         <v>75053.24656541072</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="BA32" t="n">
         <v>-20.53209160273988</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="BB32" t="n">
         <v>-34391.25343458928</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="BC32" t="n">
         <v>4800</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="BD32" t="n">
         <v>41</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BE32" t="n">
         <v>196800</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BF32" t="n">
         <v>221.4</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BG32" t="n">
         <v>1062720</v>
       </c>
-      <c r="BD32" t="n">
+      <c r="BH32" t="n">
         <v>72.29926187672825</v>
       </c>
-      <c r="BE32" t="n">
+      <c r="BI32" t="n">
         <v>347036.4570082956</v>
       </c>
-      <c r="BF32" t="n">
+      <c r="BJ32" t="n">
         <v>151.8284499411293</v>
       </c>
-      <c r="BG32" t="n">
+      <c r="BK32" t="n">
         <v>728776.5597174208</v>
       </c>
-      <c r="BH32" t="n">
+      <c r="BL32" t="n">
         <v>-69.57155005887066</v>
       </c>
-      <c r="BI32" t="n">
+      <c r="BM32" t="n">
         <v>-333943.4402825792</v>
       </c>
     </row>
@@ -5276,138 +5656,150 @@
         <v>178.7543881334982</v>
       </c>
       <c r="Q33" t="n">
+        <v>1.013090153081947</v>
+      </c>
+      <c r="R33" t="n">
         <v>0.3749644309680975</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>37.49644309680975</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>39.015</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>45.73856975381008</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>246.9882766705745</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
+        <v>1.371245975843687</v>
+      </c>
+      <c r="X33" t="n">
         <v>39.95200070978618</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
         <v>180.1196</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
         <v>-68.2338885370763</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
         <v>-27.62636731462547</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AB33" t="n">
+        <v>-0.3581558227617399</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>-26.11900629581628</v>
+      </c>
+      <c r="AD33" t="n">
         <v>29.848</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AE33" t="n">
         <v>39.38256745261761</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AF33" t="n">
         <v>-2.455557612976428</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AG33" t="n">
         <v>3150</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AH33" t="n">
         <v>34</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AI33" t="n">
         <v>107100</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AJ33" t="n">
         <v>183.6</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AK33" t="n">
         <v>578340.0000000001</v>
       </c>
-      <c r="AH33" t="n">
+      <c r="AL33" t="n">
         <v>63.2752331477846</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AM33" t="n">
         <v>199316.9844155215</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AN33" t="n">
         <v>132.8779896103477</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AO33" t="n">
         <v>418565.6672725952</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AP33" t="n">
         <v>-50.72201038965235</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AQ33" t="n">
         <v>-159774.332727405</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AR33" t="n">
         <v>1675</v>
       </c>
-      <c r="AO33" t="n">
+      <c r="AS33" t="n">
         <v>12.1</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AT33" t="n">
         <v>20267.5</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AU33" t="n">
         <v>65.34</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AV33" t="n">
         <v>109444.5</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AW33" t="n">
         <v>22.51853885553511</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AX33" t="n">
         <v>37718.5525830213</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AY33" t="n">
         <v>47.28893159662373</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AZ33" t="n">
         <v>79208.96042434474</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="BA33" t="n">
         <v>-18.05106840337628</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="BB33" t="n">
         <v>-30235.53957565526</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="BC33" t="n">
         <v>4800</v>
       </c>
-      <c r="AZ33" t="n">
+      <c r="BD33" t="n">
         <v>41</v>
       </c>
-      <c r="BA33" t="n">
+      <c r="BE33" t="n">
         <v>196800</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BF33" t="n">
         <v>221.4</v>
       </c>
-      <c r="BC33" t="n">
+      <c r="BG33" t="n">
         <v>1062720</v>
       </c>
-      <c r="BD33" t="n">
+      <c r="BH33" t="n">
         <v>76.30248703115201</v>
       </c>
-      <c r="BE33" t="n">
+      <c r="BI33" t="n">
         <v>366251.9377495297</v>
       </c>
-      <c r="BF33" t="n">
+      <c r="BJ33" t="n">
         <v>160.2352227654192</v>
       </c>
-      <c r="BG33" t="n">
+      <c r="BK33" t="n">
         <v>769129.0692740122</v>
       </c>
-      <c r="BH33" t="n">
+      <c r="BL33" t="n">
         <v>-61.16477723458078</v>
       </c>
-      <c r="BI33" t="n">
+      <c r="BM33" t="n">
         <v>-293590.9307259878</v>
       </c>
     </row>
@@ -5424,20 +5816,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>E94H6</t>
+          <t>D85B15</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E34" t="n">
-        <v>804.1636999999999</v>
+        <v>799.7073072429999</v>
       </c>
       <c r="F34" t="n">
-        <v>0.02908451</v>
+        <v>163.785652191</v>
       </c>
       <c r="G34" t="n">
-        <v>6.11</v>
+        <v>33.6023827833</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -5446,44 +5838,72 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>809</v>
+        <v>853</v>
       </c>
       <c r="M34" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="N34" t="n">
-        <v>24600</v>
+        <v>41600</v>
       </c>
       <c r="O34" t="n">
-        <v>7.552533992583436</v>
+        <v>39.39318028522861</v>
       </c>
       <c r="P34" t="n">
-        <v>15.86032138442522</v>
+        <v>212.7231735402345</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.0006966071613907628</v>
+        <v>1.298790038654702</v>
       </c>
       <c r="R34" t="n">
-        <v>0.06966071613907628</v>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
+        <v>0.421808133491262</v>
+      </c>
+      <c r="S34" t="n">
+        <v>42.1808133491262</v>
+      </c>
+      <c r="T34" t="n">
+        <v>33.6023827833</v>
+      </c>
+      <c r="U34" t="n">
+        <v>39.39318028522861</v>
+      </c>
+      <c r="V34" t="n">
+        <v>212.7231735402345</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.298790038654702</v>
+      </c>
+      <c r="X34" t="n">
+        <v>42.1808133491262</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>163.785652191</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="inlineStr"/>
@@ -5513,6 +5933,10 @@
       <c r="BG34" t="inlineStr"/>
       <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr"/>
+      <c r="BJ34" t="inlineStr"/>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5527,20 +5951,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>E94H6</t>
+          <t>D85B15</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>900</v>
       </c>
       <c r="E35" t="n">
-        <v>899.965</v>
+        <v>899.807285636</v>
       </c>
       <c r="F35" t="n">
-        <v>153.0359</v>
+        <v>211.820965147</v>
       </c>
       <c r="G35" t="n">
-        <v>59.591</v>
+        <v>42.4165475698</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -5549,44 +5973,72 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>809</v>
+        <v>853</v>
       </c>
       <c r="M35" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="N35" t="n">
-        <v>24600</v>
+        <v>41600</v>
       </c>
       <c r="O35" t="n">
-        <v>73.66007416563659</v>
+        <v>49.72631602555686</v>
       </c>
       <c r="P35" t="n">
-        <v>154.6861557478368</v>
+        <v>268.5221065380071</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.3758201332579686</v>
+        <v>1.267684274555436</v>
       </c>
       <c r="R35" t="n">
-        <v>37.58201332579686</v>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
+        <v>0.4321582376606398</v>
+      </c>
+      <c r="S35" t="n">
+        <v>43.21582376606398</v>
+      </c>
+      <c r="T35" t="n">
+        <v>42.4165475698</v>
+      </c>
+      <c r="U35" t="n">
+        <v>49.72631602555686</v>
+      </c>
+      <c r="V35" t="n">
+        <v>268.5221065380071</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.267684274555436</v>
+      </c>
+      <c r="X35" t="n">
+        <v>43.21582376606398</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>211.820965147</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="inlineStr"/>
@@ -5616,6 +6068,10 @@
       <c r="BG35" t="inlineStr"/>
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr"/>
+      <c r="BJ35" t="inlineStr"/>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5630,20 +6086,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>E94H6</t>
+          <t>D85B15</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>1000</v>
       </c>
       <c r="E36" t="n">
-        <v>999.899</v>
+        <v>999.657661495</v>
       </c>
       <c r="F36" t="n">
-        <v>182.1889</v>
+        <v>257.823580249</v>
       </c>
       <c r="G36" t="n">
-        <v>70.161</v>
+        <v>50.1537282104</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -5652,44 +6108,72 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>809</v>
+        <v>853</v>
       </c>
       <c r="M36" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="N36" t="n">
-        <v>24600</v>
+        <v>41600</v>
       </c>
       <c r="O36" t="n">
-        <v>86.72558714462299</v>
+        <v>58.79686777303634</v>
       </c>
       <c r="P36" t="n">
-        <v>182.1237330037083</v>
+        <v>317.5030859743962</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.3800086977651749</v>
+        <v>1.231474195136687</v>
       </c>
       <c r="R36" t="n">
-        <v>38.00086977651749</v>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
+        <v>0.4448653525713356</v>
+      </c>
+      <c r="S36" t="n">
+        <v>44.48653525713356</v>
+      </c>
+      <c r="T36" t="n">
+        <v>50.1537282104</v>
+      </c>
+      <c r="U36" t="n">
+        <v>58.79686777303634</v>
+      </c>
+      <c r="V36" t="n">
+        <v>317.5030859743962</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.231474195136687</v>
+      </c>
+      <c r="X36" t="n">
+        <v>44.48653525713356</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>257.823580249</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="inlineStr"/>
@@ -5719,6 +6203,10 @@
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
       <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5733,20 +6221,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>E94H6</t>
+          <t>D85B15</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>1100</v>
       </c>
       <c r="E37" t="n">
-        <v>1100.059</v>
+        <v>1099.76545523</v>
       </c>
       <c r="F37" t="n">
-        <v>236.6207</v>
+        <v>285.693787152</v>
       </c>
       <c r="G37" t="n">
-        <v>90.709</v>
+        <v>55.1783532184</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -5755,44 +6243,72 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>809</v>
+        <v>853</v>
       </c>
       <c r="M37" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="N37" t="n">
-        <v>24600</v>
+        <v>41600</v>
       </c>
       <c r="O37" t="n">
-        <v>112.1248454882571</v>
+        <v>64.68740119390387</v>
       </c>
       <c r="P37" t="n">
-        <v>235.4621755253399</v>
+        <v>349.3119664470809</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.3817418283984513</v>
+        <v>1.222679603673823</v>
       </c>
       <c r="R37" t="n">
-        <v>38.17418283984513</v>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
+        <v>0.4480652170493985</v>
+      </c>
+      <c r="S37" t="n">
+        <v>44.80652170493985</v>
+      </c>
+      <c r="T37" t="n">
+        <v>55.1783532184</v>
+      </c>
+      <c r="U37" t="n">
+        <v>64.68740119390387</v>
+      </c>
+      <c r="V37" t="n">
+        <v>349.3119664470809</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.222679603673823</v>
+      </c>
+      <c r="X37" t="n">
+        <v>44.80652170493985</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>285.693787152</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="inlineStr"/>
@@ -5822,6 +6338,10 @@
       <c r="BG37" t="inlineStr"/>
       <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr"/>
+      <c r="BJ37" t="inlineStr"/>
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="inlineStr"/>
+      <c r="BM37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5836,20 +6356,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>E94H6</t>
+          <t>D85B15</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>1200</v>
       </c>
       <c r="E38" t="n">
-        <v>1199.668</v>
+        <v>1199.86290992</v>
       </c>
       <c r="F38" t="n">
-        <v>261.7221</v>
+        <v>320.415589441</v>
       </c>
       <c r="G38" t="n">
-        <v>99.86499999999999</v>
+        <v>62.2541514527</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -5858,44 +6378,72 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>809</v>
+        <v>853</v>
       </c>
       <c r="M38" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="N38" t="n">
-        <v>24600</v>
+        <v>41600</v>
       </c>
       <c r="O38" t="n">
-        <v>123.442521631644</v>
+        <v>72.98259255885112</v>
       </c>
       <c r="P38" t="n">
-        <v>259.2292954264524</v>
+        <v>394.1059998177961</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.3835257109292667</v>
+        <v>1.229983848493006</v>
       </c>
       <c r="R38" t="n">
-        <v>38.35257109292667</v>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
+        <v>0.4454043869545165</v>
+      </c>
+      <c r="S38" t="n">
+        <v>44.54043869545165</v>
+      </c>
+      <c r="T38" t="n">
+        <v>62.2541514527</v>
+      </c>
+      <c r="U38" t="n">
+        <v>72.98259255885112</v>
+      </c>
+      <c r="V38" t="n">
+        <v>394.1059998177961</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.229983848493006</v>
+      </c>
+      <c r="X38" t="n">
+        <v>44.54043869545165</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>320.415589441</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="inlineStr"/>
@@ -5925,6 +6473,10 @@
       <c r="BG38" t="inlineStr"/>
       <c r="BH38" t="inlineStr"/>
       <c r="BI38" t="inlineStr"/>
+      <c r="BJ38" t="inlineStr"/>
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="inlineStr"/>
+      <c r="BM38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5939,20 +6491,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>E94H6</t>
+          <t>D85B15</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>1300</v>
       </c>
       <c r="E39" t="n">
-        <v>1300.024</v>
+        <v>1299.7201242</v>
       </c>
       <c r="F39" t="n">
-        <v>280.1731</v>
+        <v>346.076104124</v>
       </c>
       <c r="G39" t="n">
-        <v>107.281</v>
+        <v>67.6117271863</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -5961,44 +6513,72 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>809</v>
+        <v>853</v>
       </c>
       <c r="M39" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="N39" t="n">
-        <v>24600</v>
+        <v>41600</v>
       </c>
       <c r="O39" t="n">
-        <v>132.6093943139679</v>
+        <v>79.26345508358735</v>
       </c>
       <c r="P39" t="n">
-        <v>278.4797280593326</v>
+        <v>428.0226574513717</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.3821826927733208</v>
+        <v>1.236787667079175</v>
       </c>
       <c r="R39" t="n">
-        <v>38.21826927733208</v>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
+        <v>0.4429541275227747</v>
+      </c>
+      <c r="S39" t="n">
+        <v>44.29541275227747</v>
+      </c>
+      <c r="T39" t="n">
+        <v>67.6117271863</v>
+      </c>
+      <c r="U39" t="n">
+        <v>79.26345508358735</v>
+      </c>
+      <c r="V39" t="n">
+        <v>428.0226574513717</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.236787667079175</v>
+      </c>
+      <c r="X39" t="n">
+        <v>44.29541275227747</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>346.076104124</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="inlineStr"/>
@@ -6028,6 +6608,10 @@
       <c r="BG39" t="inlineStr"/>
       <c r="BH39" t="inlineStr"/>
       <c r="BI39" t="inlineStr"/>
+      <c r="BJ39" t="inlineStr"/>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="inlineStr"/>
+      <c r="BM39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6042,20 +6626,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>E94H6</t>
+          <t>D85B15</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>1400</v>
       </c>
       <c r="E40" t="n">
-        <v>1400.075</v>
+        <v>1399.82352181</v>
       </c>
       <c r="F40" t="n">
-        <v>300.4143</v>
+        <v>367.407812665</v>
       </c>
       <c r="G40" t="n">
-        <v>115.281</v>
+        <v>72.3903326484</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -6064,44 +6648,72 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>809</v>
+        <v>853</v>
       </c>
       <c r="M40" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="N40" t="n">
-        <v>24600</v>
+        <v>41600</v>
       </c>
       <c r="O40" t="n">
-        <v>142.4981458590853</v>
+        <v>84.8655716862837</v>
       </c>
       <c r="P40" t="n">
-        <v>299.2461063040791</v>
+        <v>458.274087105932</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.381355715969526</v>
+        <v>1.247317208041472</v>
       </c>
       <c r="R40" t="n">
-        <v>38.1355715969526</v>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="inlineStr"/>
-      <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr"/>
+        <v>0.4392148191895776</v>
+      </c>
+      <c r="S40" t="n">
+        <v>43.92148191895775</v>
+      </c>
+      <c r="T40" t="n">
+        <v>72.3903326484</v>
+      </c>
+      <c r="U40" t="n">
+        <v>84.8655716862837</v>
+      </c>
+      <c r="V40" t="n">
+        <v>458.274087105932</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.247317208041472</v>
+      </c>
+      <c r="X40" t="n">
+        <v>43.92148191895775</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>367.407812665</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="inlineStr"/>
@@ -6131,6 +6743,10 @@
       <c r="BG40" t="inlineStr"/>
       <c r="BH40" t="inlineStr"/>
       <c r="BI40" t="inlineStr"/>
+      <c r="BJ40" t="inlineStr"/>
+      <c r="BK40" t="inlineStr"/>
+      <c r="BL40" t="inlineStr"/>
+      <c r="BM40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6145,20 +6761,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>E94H6</t>
+          <t>D85B15</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>1500</v>
       </c>
       <c r="E41" t="n">
-        <v>1500.016</v>
+        <v>1499.6824457</v>
       </c>
       <c r="F41" t="n">
-        <v>301.1655</v>
+        <v>388.694464627</v>
       </c>
       <c r="G41" t="n">
-        <v>116.68</v>
+        <v>77.63584094479999</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -6167,44 +6783,72 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>809</v>
+        <v>853</v>
       </c>
       <c r="M41" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="N41" t="n">
-        <v>24600</v>
+        <v>41600</v>
       </c>
       <c r="O41" t="n">
-        <v>144.2274412855377</v>
+        <v>91.01505386260257</v>
       </c>
       <c r="P41" t="n">
-        <v>302.8776266996292</v>
+        <v>491.4812908580539</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.3777254028111073</v>
+        <v>1.264441188607331</v>
       </c>
       <c r="R41" t="n">
-        <v>37.77254028111073</v>
-      </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr"/>
+        <v>0.4332666532362657</v>
+      </c>
+      <c r="S41" t="n">
+        <v>43.32666532362657</v>
+      </c>
+      <c r="T41" t="n">
+        <v>77.63584094479999</v>
+      </c>
+      <c r="U41" t="n">
+        <v>91.01505386260257</v>
+      </c>
+      <c r="V41" t="n">
+        <v>491.4812908580539</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.264441188607331</v>
+      </c>
+      <c r="X41" t="n">
+        <v>43.32666532362657</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>388.694464627</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="inlineStr"/>
@@ -6234,6 +6878,10 @@
       <c r="BG41" t="inlineStr"/>
       <c r="BH41" t="inlineStr"/>
       <c r="BI41" t="inlineStr"/>
+      <c r="BJ41" t="inlineStr"/>
+      <c r="BK41" t="inlineStr"/>
+      <c r="BL41" t="inlineStr"/>
+      <c r="BM41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6248,20 +6896,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>E94H6</t>
+          <t>D85B15</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>1600</v>
       </c>
       <c r="E42" t="n">
-        <v>1600.038</v>
+        <v>1599.77762091</v>
       </c>
       <c r="F42" t="n">
-        <v>300.3554</v>
+        <v>394.333284808</v>
       </c>
       <c r="G42" t="n">
-        <v>117.308</v>
+        <v>79.76341055490001</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -6270,44 +6918,72 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>809</v>
+        <v>853</v>
       </c>
       <c r="M42" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="N42" t="n">
-        <v>24600</v>
+        <v>41600</v>
       </c>
       <c r="O42" t="n">
-        <v>145.0037082818294</v>
+        <v>93.50927380410317</v>
       </c>
       <c r="P42" t="n">
-        <v>304.5077873918418</v>
+        <v>504.9500785421571</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.3746926789348365</v>
+        <v>1.280515994961004</v>
       </c>
       <c r="R42" t="n">
-        <v>37.46926789348365</v>
-      </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
+        <v>0.427827691460166</v>
+      </c>
+      <c r="S42" t="n">
+        <v>42.7827691460166</v>
+      </c>
+      <c r="T42" t="n">
+        <v>79.76341055490001</v>
+      </c>
+      <c r="U42" t="n">
+        <v>93.50927380410317</v>
+      </c>
+      <c r="V42" t="n">
+        <v>504.9500785421571</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.280515994961004</v>
+      </c>
+      <c r="X42" t="n">
+        <v>42.7827691460166</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>394.333284808</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="inlineStr"/>
@@ -6337,6 +7013,10 @@
       <c r="BG42" t="inlineStr"/>
       <c r="BH42" t="inlineStr"/>
       <c r="BI42" t="inlineStr"/>
+      <c r="BJ42" t="inlineStr"/>
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="inlineStr"/>
+      <c r="BM42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6351,20 +7031,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>E94H6</t>
+          <t>D85B15</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>1700</v>
       </c>
       <c r="E43" t="n">
-        <v>1699.999</v>
+        <v>1699.63841723</v>
       </c>
       <c r="F43" t="n">
-        <v>296.0968</v>
+        <v>392.44891672</v>
       </c>
       <c r="G43" t="n">
-        <v>117.119</v>
+        <v>79.86487850029999</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -6373,44 +7053,72 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>809</v>
+        <v>853</v>
       </c>
       <c r="M43" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="N43" t="n">
-        <v>24600</v>
+        <v>41600</v>
       </c>
       <c r="O43" t="n">
-        <v>144.770086526576</v>
+        <v>93.62822801910902</v>
       </c>
       <c r="P43" t="n">
-        <v>304.0171817058097</v>
+        <v>505.5924313031887</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.3699761697452185</v>
+        <v>1.288301253393223</v>
       </c>
       <c r="R43" t="n">
-        <v>36.99761697452185</v>
-      </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
+        <v>0.4252423108019509</v>
+      </c>
+      <c r="S43" t="n">
+        <v>42.52423108019509</v>
+      </c>
+      <c r="T43" t="n">
+        <v>79.86487850029999</v>
+      </c>
+      <c r="U43" t="n">
+        <v>93.62822801910902</v>
+      </c>
+      <c r="V43" t="n">
+        <v>505.5924313031887</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.288301253393223</v>
+      </c>
+      <c r="X43" t="n">
+        <v>42.52423108019509</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>392.44891672</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="inlineStr"/>
@@ -6440,6 +7148,10 @@
       <c r="BG43" t="inlineStr"/>
       <c r="BH43" t="inlineStr"/>
       <c r="BI43" t="inlineStr"/>
+      <c r="BJ43" t="inlineStr"/>
+      <c r="BK43" t="inlineStr"/>
+      <c r="BL43" t="inlineStr"/>
+      <c r="BM43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6454,20 +7166,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>E94H6</t>
+          <t>D85B15</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>1800</v>
       </c>
       <c r="E44" t="n">
-        <v>1799.979</v>
+        <v>1799.73595333</v>
       </c>
       <c r="F44" t="n">
-        <v>291.8231</v>
+        <v>394.618160262</v>
       </c>
       <c r="G44" t="n">
-        <v>116.542</v>
+        <v>81.3583114385</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -6476,44 +7188,72 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>809</v>
+        <v>853</v>
       </c>
       <c r="M44" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="N44" t="n">
-        <v>24600</v>
+        <v>41600</v>
       </c>
       <c r="O44" t="n">
-        <v>144.0568603213844</v>
+        <v>95.37902865005861</v>
       </c>
       <c r="P44" t="n">
-        <v>302.5194066749073</v>
+        <v>515.0467547103166</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.3664414503972399</v>
+        <v>1.305177527482162</v>
       </c>
       <c r="R44" t="n">
-        <v>36.64414503972399</v>
-      </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr"/>
+        <v>0.4197438206424157</v>
+      </c>
+      <c r="S44" t="n">
+        <v>41.97438206424157</v>
+      </c>
+      <c r="T44" t="n">
+        <v>81.3583114385</v>
+      </c>
+      <c r="U44" t="n">
+        <v>95.37902865005861</v>
+      </c>
+      <c r="V44" t="n">
+        <v>515.0467547103166</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.305177527482162</v>
+      </c>
+      <c r="X44" t="n">
+        <v>41.97438206424157</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>394.618160262</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr"/>
@@ -6543,6 +7283,2669 @@
       <c r="BG44" t="inlineStr"/>
       <c r="BH44" t="inlineStr"/>
       <c r="BI44" t="inlineStr"/>
+      <c r="BJ44" t="inlineStr"/>
+      <c r="BK44" t="inlineStr"/>
+      <c r="BL44" t="inlineStr"/>
+      <c r="BM44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>D85B15</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1900</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1899.83674582</v>
+      </c>
+      <c r="F45" t="n">
+        <v>395.840338659</v>
+      </c>
+      <c r="G45" t="n">
+        <v>83.03258260769999</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>853</v>
+      </c>
+      <c r="M45" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N45" t="n">
+        <v>41600</v>
+      </c>
+      <c r="O45" t="n">
+        <v>97.341831896483</v>
+      </c>
+      <c r="P45" t="n">
+        <v>525.6458922410083</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.32792401608627</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.4125538776055943</v>
+      </c>
+      <c r="S45" t="n">
+        <v>41.25538776055943</v>
+      </c>
+      <c r="T45" t="n">
+        <v>83.03258260769999</v>
+      </c>
+      <c r="U45" t="n">
+        <v>97.341831896483</v>
+      </c>
+      <c r="V45" t="n">
+        <v>525.6458922410083</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.32792401608627</v>
+      </c>
+      <c r="X45" t="n">
+        <v>41.25538776055943</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>395.840338659</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
+      <c r="BA45" t="inlineStr"/>
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="inlineStr"/>
+      <c r="BD45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr"/>
+      <c r="BF45" t="inlineStr"/>
+      <c r="BG45" t="inlineStr"/>
+      <c r="BH45" t="inlineStr"/>
+      <c r="BI45" t="inlineStr"/>
+      <c r="BJ45" t="inlineStr"/>
+      <c r="BK45" t="inlineStr"/>
+      <c r="BL45" t="inlineStr"/>
+      <c r="BM45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>D85B15</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1999.68695886</v>
+      </c>
+      <c r="F46" t="n">
+        <v>382.336770997</v>
+      </c>
+      <c r="G46" t="n">
+        <v>81.04507697379999</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>853</v>
+      </c>
+      <c r="M46" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N46" t="n">
+        <v>41600</v>
+      </c>
+      <c r="O46" t="n">
+        <v>95.01181356834701</v>
+      </c>
+      <c r="P46" t="n">
+        <v>513.0637932690739</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.341915902912461</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.4082522614218711</v>
+      </c>
+      <c r="S46" t="n">
+        <v>40.82522614218711</v>
+      </c>
+      <c r="T46" t="n">
+        <v>81.04507697379999</v>
+      </c>
+      <c r="U46" t="n">
+        <v>95.01181356834701</v>
+      </c>
+      <c r="V46" t="n">
+        <v>513.0637932690739</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.341915902912461</v>
+      </c>
+      <c r="X46" t="n">
+        <v>40.82522614218711</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>382.336770997</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="inlineStr"/>
+      <c r="BH46" t="inlineStr"/>
+      <c r="BI46" t="inlineStr"/>
+      <c r="BJ46" t="inlineStr"/>
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="inlineStr"/>
+      <c r="BM46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>D85B15</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2099.79556669</v>
+      </c>
+      <c r="F47" t="n">
+        <v>349.060569711</v>
+      </c>
+      <c r="G47" t="n">
+        <v>77.42179575759999</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>853</v>
+      </c>
+      <c r="M47" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N47" t="n">
+        <v>41600</v>
+      </c>
+      <c r="O47" t="n">
+        <v>90.76412163845251</v>
+      </c>
+      <c r="P47" t="n">
+        <v>490.1262568476436</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.404129539046581</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.3901635759147786</v>
+      </c>
+      <c r="S47" t="n">
+        <v>39.01635759147786</v>
+      </c>
+      <c r="T47" t="n">
+        <v>77.42179575759999</v>
+      </c>
+      <c r="U47" t="n">
+        <v>90.76412163845251</v>
+      </c>
+      <c r="V47" t="n">
+        <v>490.1262568476436</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.404129539046581</v>
+      </c>
+      <c r="X47" t="n">
+        <v>39.01635759147786</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>349.060569711</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
+      <c r="BA47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="inlineStr"/>
+      <c r="BG47" t="inlineStr"/>
+      <c r="BH47" t="inlineStr"/>
+      <c r="BI47" t="inlineStr"/>
+      <c r="BJ47" t="inlineStr"/>
+      <c r="BK47" t="inlineStr"/>
+      <c r="BL47" t="inlineStr"/>
+      <c r="BM47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>D85B15</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2199.65164124</v>
+      </c>
+      <c r="F48" t="n">
+        <v>288.565104075</v>
+      </c>
+      <c r="G48" t="n">
+        <v>66.5179478619</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15.xlsx</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>853</v>
+      </c>
+      <c r="M48" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N48" t="n">
+        <v>41600</v>
+      </c>
+      <c r="O48" t="n">
+        <v>77.98118154970692</v>
+      </c>
+      <c r="P48" t="n">
+        <v>421.0983803684174</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.45928379565594</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.3754171763112966</v>
+      </c>
+      <c r="S48" t="n">
+        <v>37.54171763112966</v>
+      </c>
+      <c r="T48" t="n">
+        <v>66.5179478619</v>
+      </c>
+      <c r="U48" t="n">
+        <v>77.98118154970692</v>
+      </c>
+      <c r="V48" t="n">
+        <v>421.0983803684174</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.45928379565594</v>
+      </c>
+      <c r="X48" t="n">
+        <v>37.54171763112966</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>288.565104075</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr"/>
+      <c r="BA48" t="inlineStr"/>
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="inlineStr"/>
+      <c r="BD48" t="inlineStr"/>
+      <c r="BE48" t="inlineStr"/>
+      <c r="BF48" t="inlineStr"/>
+      <c r="BG48" t="inlineStr"/>
+      <c r="BH48" t="inlineStr"/>
+      <c r="BI48" t="inlineStr"/>
+      <c r="BJ48" t="inlineStr"/>
+      <c r="BK48" t="inlineStr"/>
+      <c r="BL48" t="inlineStr"/>
+      <c r="BM48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>804</v>
+      </c>
+      <c r="E49" t="n">
+        <v>804.1636999999999</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.02908451</v>
+      </c>
+      <c r="G49" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>809</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O49" t="n">
+        <v>7.552533992583436</v>
+      </c>
+      <c r="P49" t="n">
+        <v>15.86032138442522</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>545.3185006185497</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.0006966071613907628</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.06966071613907628</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
+      <c r="BA49" t="inlineStr"/>
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="inlineStr"/>
+      <c r="BD49" t="inlineStr"/>
+      <c r="BE49" t="inlineStr"/>
+      <c r="BF49" t="inlineStr"/>
+      <c r="BG49" t="inlineStr"/>
+      <c r="BH49" t="inlineStr"/>
+      <c r="BI49" t="inlineStr"/>
+      <c r="BJ49" t="inlineStr"/>
+      <c r="BK49" t="inlineStr"/>
+      <c r="BL49" t="inlineStr"/>
+      <c r="BM49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>900</v>
+      </c>
+      <c r="E50" t="n">
+        <v>899.965</v>
+      </c>
+      <c r="F50" t="n">
+        <v>153.0359</v>
+      </c>
+      <c r="G50" t="n">
+        <v>59.591</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>809</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O50" t="n">
+        <v>73.66007416563659</v>
+      </c>
+      <c r="P50" t="n">
+        <v>154.6861557478368</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.010783455044449</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.3758201332579686</v>
+      </c>
+      <c r="S50" t="n">
+        <v>37.58201332579686</v>
+      </c>
+      <c r="T50" t="n">
+        <v>42.4165475698</v>
+      </c>
+      <c r="U50" t="n">
+        <v>49.72631602555686</v>
+      </c>
+      <c r="V50" t="n">
+        <v>268.5221065380071</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.267684274555436</v>
+      </c>
+      <c r="X50" t="n">
+        <v>43.21582376606398</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>211.820965147</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-113.8359507901702</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-42.39351175135284</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>-0.256900819510987</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>-20.2653629667434</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>17.1744524302</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>23.93375814007972</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>-5.633810440267112</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>107100</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>578340.0000000001</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>50.3645297259601</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>158648.2686367743</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>105.7655124245162</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>333161.364137226</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>-77.83448757548382</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>-245178.6358627741</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>1675</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>20267.5</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>109444.5</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>17.9238473436505</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>30022.4443006146</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>37.64007942166606</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>63047.13303129065</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>-27.69992057833394</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>-46397.36696870935</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>4800</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>196800</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>221.4</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>1062720</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>60.73369761071658</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>291521.7485314396</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>127.5407649825048</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>612195.6719160231</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>-93.85923501749519</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>-450524.3280839769</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E51" t="n">
+        <v>999.899</v>
+      </c>
+      <c r="F51" t="n">
+        <v>182.1889</v>
+      </c>
+      <c r="G51" t="n">
+        <v>70.161</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>809</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O51" t="n">
+        <v>86.72558714462299</v>
+      </c>
+      <c r="P51" t="n">
+        <v>182.1237330037083</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.9996423108307273</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.3800086977651749</v>
+      </c>
+      <c r="S51" t="n">
+        <v>38.00086977651749</v>
+      </c>
+      <c r="T51" t="n">
+        <v>50.1537282104</v>
+      </c>
+      <c r="U51" t="n">
+        <v>58.79686777303634</v>
+      </c>
+      <c r="V51" t="n">
+        <v>317.5030859743962</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.231474195136687</v>
+      </c>
+      <c r="X51" t="n">
+        <v>44.48653525713356</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>257.823580249</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-135.379352970688</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-42.63875185818039</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>-0.2318318843059595</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>-18.82555763015622</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>20.0072717896</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>27.92871937158665</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>-6.485665480616071</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>107100</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>578340.0000000001</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>50.15011980399086</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>157972.8773825712</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>105.3152515883808</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>331743.0425033996</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>-78.2847484116192</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>-246596.9574966005</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1675</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>20267.5</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>109444.5</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>17.84754263612616</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>29894.63391551131</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>37.47983953586493</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>62778.73122257376</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>-27.86016046413507</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>-46665.76877742624</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>4800</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>196800</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>221.4</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>1062720</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>60.47514446951838</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>290280.6934536882</v>
+      </c>
+      <c r="BJ51" t="n">
+        <v>126.9978033859886</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>609589.4562527454</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>-94.40219661401139</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>-453130.5437472546</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1100.059</v>
+      </c>
+      <c r="F52" t="n">
+        <v>236.6207</v>
+      </c>
+      <c r="G52" t="n">
+        <v>90.709</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>809</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O52" t="n">
+        <v>112.1248454882571</v>
+      </c>
+      <c r="P52" t="n">
+        <v>235.4621755253399</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.9951038752118473</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.3817418283984513</v>
+      </c>
+      <c r="S52" t="n">
+        <v>38.17418283984513</v>
+      </c>
+      <c r="T52" t="n">
+        <v>55.1783532184</v>
+      </c>
+      <c r="U52" t="n">
+        <v>64.68740119390387</v>
+      </c>
+      <c r="V52" t="n">
+        <v>349.3119664470809</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.222679603673823</v>
+      </c>
+      <c r="X52" t="n">
+        <v>44.80652170493985</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>285.693787152</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-113.849790921741</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-32.5925825215005</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>-0.2275757284619757</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>-18.61286699951254</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>35.53064678160001</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>47.43744429435324</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>-6.632338865094717</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>107100</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>578340.0000000001</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>58.93334213834528</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>185640.0277357876</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>123.7600184905251</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>389844.058245154</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>-59.83998150947492</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>-188495.9417548461</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>1675</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>20267.5</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>109444.5</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>20.9733364668817</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>35130.33858202685</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>44.04400658045157</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>73773.71102225638</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>-21.29599341954843</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>-35670.78897774362</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>4800</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>196800</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>221.4</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>1062720</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>71.06667728447519</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>341120.0509654809</v>
+      </c>
+      <c r="BJ52" t="n">
+        <v>149.2400222973979</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>716352.1070275099</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>-72.15997770260211</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>-346367.8929724901</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1199.668</v>
+      </c>
+      <c r="F53" t="n">
+        <v>261.7221</v>
+      </c>
+      <c r="G53" t="n">
+        <v>99.86499999999999</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>809</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O53" t="n">
+        <v>123.442521631644</v>
+      </c>
+      <c r="P53" t="n">
+        <v>259.2292954264524</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.9904753760819295</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.3835257109292667</v>
+      </c>
+      <c r="S53" t="n">
+        <v>38.35257109292667</v>
+      </c>
+      <c r="T53" t="n">
+        <v>62.2541514527</v>
+      </c>
+      <c r="U53" t="n">
+        <v>72.98259255885112</v>
+      </c>
+      <c r="V53" t="n">
+        <v>394.1059998177961</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.229983848493006</v>
+      </c>
+      <c r="X53" t="n">
+        <v>44.54043869545165</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>320.415589441</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-134.8767043913437</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-34.22345877852664</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>-0.2395084724110762</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>-19.47248922858016</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>37.61084854729999</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>50.45992907279287</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>-6.187867602524982</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>107100</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>578340.0000000001</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>57.50749032505957</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>181148.5945239376</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>120.7657296826251</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>380412.0485002691</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>-62.83427031737492</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>-197927.951499731</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>1675</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>20267.5</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>109444.5</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>20.46590096862414</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>34280.38412244544</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>42.9783920341107</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>71988.80665713541</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>-22.36160796588931</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>-37455.69334286459</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>4800</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>196800</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>221.4</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>1062720</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>69.34726774492478</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>332866.8851756389</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>145.629262264342</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>699020.4588688418</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>-75.77073773565797</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>-363699.5411311582</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1300.024</v>
+      </c>
+      <c r="F54" t="n">
+        <v>280.1731</v>
+      </c>
+      <c r="G54" t="n">
+        <v>107.281</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>809</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O54" t="n">
+        <v>132.6093943139679</v>
+      </c>
+      <c r="P54" t="n">
+        <v>278.4797280593326</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.9939559795688186</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.3821826927733208</v>
+      </c>
+      <c r="S54" t="n">
+        <v>38.21826927733208</v>
+      </c>
+      <c r="T54" t="n">
+        <v>67.6117271863</v>
+      </c>
+      <c r="U54" t="n">
+        <v>79.26345508358735</v>
+      </c>
+      <c r="V54" t="n">
+        <v>428.0226574513717</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.236787667079175</v>
+      </c>
+      <c r="X54" t="n">
+        <v>44.29541275227747</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>346.076104124</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-149.5429293920391</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-34.9380872224104</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>-0.2428316875103567</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>-19.63406443757911</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>39.6692728137</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>53.34593923038052</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>-6.077143474945395</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>107100</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>578340.0000000001</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>56.88270088554977</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>179180.5077894818</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>119.4536718596545</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>376279.0663579117</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>-64.1463281403455</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>-202060.9336420884</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1675</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>20267.5</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>109444.5</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>20.24354943279859</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>33907.94529993764</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>42.51145380887705</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>71206.68512986906</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>-22.82854619112295</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>-38237.81487013094</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>4800</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>196800</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>221.4</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>1062720</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>68.5938451855159</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>329250.4568904763</v>
+      </c>
+      <c r="BJ54" t="n">
+        <v>144.0470748895834</v>
+      </c>
+      <c r="BK54" t="n">
+        <v>691425.9594700004</v>
+      </c>
+      <c r="BL54" t="n">
+        <v>-77.35292511041661</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>-371294.0405299996</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1400.075</v>
+      </c>
+      <c r="F55" t="n">
+        <v>300.4143</v>
+      </c>
+      <c r="G55" t="n">
+        <v>115.281</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>809</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O55" t="n">
+        <v>142.4981458590853</v>
+      </c>
+      <c r="P55" t="n">
+        <v>299.2461063040791</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.9961113911823742</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.381355715969526</v>
+      </c>
+      <c r="S55" t="n">
+        <v>38.1355715969526</v>
+      </c>
+      <c r="T55" t="n">
+        <v>72.3903326484</v>
+      </c>
+      <c r="U55" t="n">
+        <v>84.8655716862837</v>
+      </c>
+      <c r="V55" t="n">
+        <v>458.274087105932</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.247317208041472</v>
+      </c>
+      <c r="X55" t="n">
+        <v>43.92148191895775</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>367.407812665</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-159.0279808018529</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-34.70149966500132</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>-0.251205816859098</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>-20.13968982706007</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>42.8906673516</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>57.6325741728016</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>-5.785910322005151</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>107100</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>578340.0000000001</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>57.08954600717028</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>179832.0699225864</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>119.8880466150576</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>377647.3468374314</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>-63.71195338494243</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>-200692.6531625687</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1675</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>20267.5</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>109444.5</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>20.31716196137531</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>34031.24628530363</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>42.66604011888814</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>71465.61719913763</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>-22.67395988111186</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>-37978.88280086237</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>4800</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>196800</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>221.4</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>1062720</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>68.84327606747003</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>330447.7251238562</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>144.5708797416871</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>693940.2227600979</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>-76.82912025831294</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>-368779.7772399021</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1500.016</v>
+      </c>
+      <c r="F56" t="n">
+        <v>301.1655</v>
+      </c>
+      <c r="G56" t="n">
+        <v>116.68</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>809</v>
+      </c>
+      <c r="M56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O56" t="n">
+        <v>144.2274412855377</v>
+      </c>
+      <c r="P56" t="n">
+        <v>302.8776266996292</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1.00568500276303</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.3777254028111073</v>
+      </c>
+      <c r="S56" t="n">
+        <v>37.77254028111073</v>
+      </c>
+      <c r="T56" t="n">
+        <v>77.63584094479999</v>
+      </c>
+      <c r="U56" t="n">
+        <v>91.01505386260257</v>
+      </c>
+      <c r="V56" t="n">
+        <v>491.4812908580539</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.264441188607331</v>
+      </c>
+      <c r="X56" t="n">
+        <v>43.32666532362657</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>388.694464627</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-188.6036641584247</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-38.37453585041873</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>-0.2587561858443008</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>-20.46407442083548</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>39.04415905520001</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>53.21238742293514</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>-5.554125042515842</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>107100</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>578340.0000000001</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>53.87826294220535</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>169716.5282679469</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>113.1443521786312</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>356404.7093626884</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>-70.45564782136879</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>-221935.2906373117</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>1675</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>20267.5</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>109444.5</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>19.17432298825543</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>32116.99100532785</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>40.26607827533641</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>67445.68111118849</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>-25.07392172466359</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>-41998.81888881151</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>4800</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>196800</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>221.4</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>1062720</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>64.97084648912997</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>311860.0631478239</v>
+      </c>
+      <c r="BJ56" t="n">
+        <v>136.438777627173</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>654906.1326104301</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>-84.96122237282705</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>-407813.8673895699</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1600.038</v>
+      </c>
+      <c r="F57" t="n">
+        <v>300.3554</v>
+      </c>
+      <c r="G57" t="n">
+        <v>117.308</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>809</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O57" t="n">
+        <v>145.0037082818294</v>
+      </c>
+      <c r="P57" t="n">
+        <v>304.5077873918418</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1.013824913392074</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.3746926789348365</v>
+      </c>
+      <c r="S57" t="n">
+        <v>37.46926789348365</v>
+      </c>
+      <c r="T57" t="n">
+        <v>79.76341055490001</v>
+      </c>
+      <c r="U57" t="n">
+        <v>93.50927380410317</v>
+      </c>
+      <c r="V57" t="n">
+        <v>504.9500785421571</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.280515994961004</v>
+      </c>
+      <c r="X57" t="n">
+        <v>42.7827691460166</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>394.333284808</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-200.4422911503153</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-39.69546687249021</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>-0.2666910815689301</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>-20.8268450076683</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>37.5445894451</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>51.49443447772626</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>-5.313501252532944</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>107100</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>578340.0000000001</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>52.72339182005142</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>166078.684233162</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>110.719122822108</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>348765.2368896401</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>-72.88087717789205</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>-229574.76311036</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1675</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>20267.5</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>109444.5</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>18.76332473595947</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>31428.56893273212</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>39.4029819455149</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>65999.99475873745</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>-25.93701805448511</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>-43444.50524126255</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>4800</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>196800</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>221.4</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>1062720</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>63.57820778300318</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>305175.3973584152</v>
+      </c>
+      <c r="BJ57" t="n">
+        <v>133.5142363443067</v>
+      </c>
+      <c r="BK57" t="n">
+        <v>640868.334452672</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>-87.88576365569332</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>-421851.665547328</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1699.999</v>
+      </c>
+      <c r="F58" t="n">
+        <v>296.0968</v>
+      </c>
+      <c r="G58" t="n">
+        <v>117.119</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>809</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O58" t="n">
+        <v>144.770086526576</v>
+      </c>
+      <c r="P58" t="n">
+        <v>304.0171817058097</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1.026749298559828</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.3699761697452185</v>
+      </c>
+      <c r="S58" t="n">
+        <v>36.99761697452185</v>
+      </c>
+      <c r="T58" t="n">
+        <v>79.86487850029999</v>
+      </c>
+      <c r="U58" t="n">
+        <v>93.62822801910902</v>
+      </c>
+      <c r="V58" t="n">
+        <v>505.5924313031887</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.288301253393223</v>
+      </c>
+      <c r="X58" t="n">
+        <v>42.52423108019509</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>392.44891672</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-201.5752495973791</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-39.86911929789162</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>-0.2615519548333953</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>-20.30208028941215</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>37.25412149970001</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>51.14185850746701</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>-5.526614105673239</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>107100</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>578340.0000000001</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>52.5715699852719</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>165600.4454536065</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>110.400296969071</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>347760.9354525736</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>-73.19970303092903</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>-230579.0645474265</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>1675</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>20267.5</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>109444.5</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>18.70929402417029</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>31338.06749048523</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>39.28951745075761</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>65809.94173001901</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>-26.05048254924239</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>-43634.55826998099</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>4800</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>196800</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>221.4</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>1062720</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>63.39512851165141</v>
+      </c>
+      <c r="BI58" t="n">
+        <v>304296.6168559268</v>
+      </c>
+      <c r="BJ58" t="n">
+        <v>133.129769874468</v>
+      </c>
+      <c r="BK58" t="n">
+        <v>639022.8953974462</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>-88.27023012553204</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>-423697.1046025538</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SWay_P8_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>E94H6</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1799.979</v>
+      </c>
+      <c r="F59" t="n">
+        <v>291.8231</v>
+      </c>
+      <c r="G59" t="n">
+        <v>116.542</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>P251191_C13_Etanol_Full_Load_Curve_Rev_26.xlsx</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>809</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>24600</v>
+      </c>
+      <c r="O59" t="n">
+        <v>144.0568603213844</v>
+      </c>
+      <c r="P59" t="n">
+        <v>302.5194066749073</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1.036653392671476</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.3664414503972399</v>
+      </c>
+      <c r="S59" t="n">
+        <v>36.64414503972399</v>
+      </c>
+      <c r="T59" t="n">
+        <v>81.3583114385</v>
+      </c>
+      <c r="U59" t="n">
+        <v>95.37902865005861</v>
+      </c>
+      <c r="V59" t="n">
+        <v>515.0467547103166</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.305177527482162</v>
+      </c>
+      <c r="X59" t="n">
+        <v>41.97438206424157</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>394.618160262</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-212.5273480354093</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-41.26370006057864</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>-0.2685241348106859</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>-20.57376327408119</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>35.18368856150001</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>48.67783167132581</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>-5.330237024517579</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>107100</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>578340.0000000001</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>51.35230794703696</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>161759.7700331664</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>107.8398466887776</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>339695.5170696495</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>-75.7601533112224</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>-238644.4829303506</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>1675</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>20267.5</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>109444.5</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>18.27538018115139</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>30611.26180342857</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>38.37829838041792</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>64283.64978720001</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>-26.96170161958209</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>-45160.85021279999</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>4800</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>196800</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>221.4</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>1062720</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>61.9248419361328</v>
+      </c>
+      <c r="BI59" t="n">
+        <v>297239.2412934374</v>
+      </c>
+      <c r="BJ59" t="n">
+        <v>130.0421680658789</v>
+      </c>
+      <c r="BK59" t="n">
+        <v>624202.4067162187</v>
+      </c>
+      <c r="BL59" t="n">
+        <v>-91.35783193412112</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>-438517.5932837813</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/out_FPT/lv_kpis_fpt.xlsx
+++ b/out_FPT/lv_kpis_fpt.xlsx
@@ -9257,7 +9257,7 @@
         <v>627.277016368</v>
       </c>
       <c r="K34" t="n">
-        <v>-1156.3964032</v>
+        <v>-1.1563964032</v>
       </c>
       <c r="L34" t="n">
         <v>1034.9514585</v>
@@ -9317,12 +9317,18 @@
       <c r="AK34" t="n">
         <v>3.829865485631768</v>
       </c>
-      <c r="AL34" t="inlineStr"/>
+      <c r="AL34" t="n">
+        <v>1011.8436035968</v>
+      </c>
       <c r="AM34" t="n">
         <v>2047.9514585</v>
       </c>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
+      <c r="AN34" t="n">
+        <v>2.023980238863148</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0.1454833817573361</v>
+      </c>
       <c r="AP34" t="n">
         <v>19.05097450444929</v>
       </c>
@@ -9488,7 +9494,7 @@
         <v>818.1010032</v>
       </c>
       <c r="K35" t="n">
-        <v>-6294.4706135</v>
+        <v>-6.2944706135</v>
       </c>
       <c r="L35" t="n">
         <v>1398.00725894</v>
@@ -9548,12 +9554,18 @@
       <c r="AK35" t="n">
         <v>3.862228663873061</v>
       </c>
-      <c r="AL35" t="inlineStr"/>
+      <c r="AL35" t="n">
+        <v>1006.7055293865</v>
+      </c>
       <c r="AM35" t="n">
         <v>2411.00725894</v>
       </c>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr"/>
+      <c r="AN35" t="n">
+        <v>2.394947865647763</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0.1906927639437788</v>
+      </c>
       <c r="AP35" t="n">
         <v>21.89822905972583</v>
       </c>
@@ -9719,7 +9731,7 @@
         <v>1066.51589024</v>
       </c>
       <c r="K36" t="n">
-        <v>-14442.089451</v>
+        <v>-14.442089451</v>
       </c>
       <c r="L36" t="n">
         <v>1830.33291581</v>
@@ -9779,12 +9791,18 @@
       <c r="AK36" t="n">
         <v>4.136611124591413</v>
       </c>
-      <c r="AL36" t="inlineStr"/>
+      <c r="AL36" t="n">
+        <v>998.557910549</v>
+      </c>
       <c r="AM36" t="n">
         <v>2843.33291581</v>
       </c>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
+      <c r="AN36" t="n">
+        <v>2.847439177810685</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0.2506917189847213</v>
+      </c>
       <c r="AP36" t="n">
         <v>23.99181376145656</v>
       </c>
@@ -9950,7 +9968,7 @@
         <v>1268.3126194</v>
       </c>
       <c r="K37" t="n">
-        <v>-22964.544246</v>
+        <v>-22.964544246</v>
       </c>
       <c r="L37" t="n">
         <v>2095.37852895</v>
@@ -10010,12 +10028,18 @@
       <c r="AK37" t="n">
         <v>4.439412673420192</v>
       </c>
-      <c r="AL37" t="inlineStr"/>
+      <c r="AL37" t="n">
+        <v>990.0354557540001</v>
+      </c>
       <c r="AM37" t="n">
         <v>3108.37852895</v>
       </c>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
+      <c r="AN37" t="n">
+        <v>3.139663848283791</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0.3006765122493675</v>
+      </c>
       <c r="AP37" t="n">
         <v>24.16508335106959</v>
       </c>
@@ -10181,7 +10205,7 @@
         <v>1394.40211569</v>
       </c>
       <c r="K38" t="n">
-        <v>-29096.393968</v>
+        <v>-29.096393968</v>
       </c>
       <c r="L38" t="n">
         <v>2137.22319898</v>
@@ -10241,12 +10265,18 @@
       <c r="AK38" t="n">
         <v>4.351854783728491</v>
       </c>
-      <c r="AL38" t="inlineStr"/>
+      <c r="AL38" t="n">
+        <v>983.903606032</v>
+      </c>
       <c r="AM38" t="n">
         <v>3150.22319898</v>
       </c>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr"/>
+      <c r="AN38" t="n">
+        <v>3.201759989156442</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0.3326502254066982</v>
+      </c>
       <c r="AP38" t="n">
         <v>24.84139032717415</v>
       </c>
@@ -10412,7 +10442,7 @@
         <v>1501.12002116</v>
       </c>
       <c r="K39" t="n">
-        <v>-34923.184546</v>
+        <v>-34.923184546</v>
       </c>
       <c r="L39" t="n">
         <v>2152.74799384</v>
@@ -10472,12 +10502,18 @@
       <c r="AK39" t="n">
         <v>4.337543110523877</v>
       </c>
-      <c r="AL39" t="inlineStr"/>
+      <c r="AL39" t="n">
+        <v>978.076815454</v>
+      </c>
       <c r="AM39" t="n">
         <v>3165.74799384</v>
       </c>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
+      <c r="AN39" t="n">
+        <v>3.236706916900525</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0.3601964987750724</v>
+      </c>
       <c r="AP39" t="n">
         <v>24.76891804962357</v>
       </c>
@@ -10643,7 +10679,7 @@
         <v>1591.65581007</v>
       </c>
       <c r="K40" t="n">
-        <v>-40246.56739800001</v>
+        <v>-40.246567398</v>
       </c>
       <c r="L40" t="n">
         <v>2140.61126823</v>
@@ -10703,12 +10739,18 @@
       <c r="AK40" t="n">
         <v>4.332122930443129</v>
       </c>
-      <c r="AL40" t="inlineStr"/>
+      <c r="AL40" t="n">
+        <v>972.753432602</v>
+      </c>
       <c r="AM40" t="n">
         <v>3153.61126823</v>
       </c>
-      <c r="AN40" t="inlineStr"/>
-      <c r="AO40" t="inlineStr"/>
+      <c r="AN40" t="n">
+        <v>3.241943089107858</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0.3841165943639843</v>
+      </c>
       <c r="AP40" t="n">
         <v>24.41601073126204</v>
       </c>
@@ -10874,7 +10916,7 @@
         <v>1689.92398591</v>
       </c>
       <c r="K41" t="n">
-        <v>-46450.178517</v>
+        <v>-46.450178517</v>
       </c>
       <c r="L41" t="n">
         <v>2156.00222406</v>
@@ -10934,12 +10976,18 @@
       <c r="AK41" t="n">
         <v>4.347692441495634</v>
       </c>
-      <c r="AL41" t="inlineStr"/>
+      <c r="AL41" t="n">
+        <v>966.549821483</v>
+      </c>
       <c r="AM41" t="n">
         <v>3169.00222406</v>
       </c>
-      <c r="AN41" t="inlineStr"/>
-      <c r="AO41" t="inlineStr"/>
+      <c r="AN41" t="n">
+        <v>3.278674470393804</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0.4104028682278533</v>
+      </c>
       <c r="AP41" t="n">
         <v>24.11053782113172</v>
       </c>
@@ -11105,7 +11153,7 @@
         <v>1757.33848801</v>
       </c>
       <c r="K42" t="n">
-        <v>-50615.731116</v>
+        <v>-50.615731116</v>
       </c>
       <c r="L42" t="n">
         <v>2075.32321525</v>
@@ -11165,12 +11213,18 @@
       <c r="AK42" t="n">
         <v>4.456480230588814</v>
       </c>
-      <c r="AL42" t="inlineStr"/>
+      <c r="AL42" t="n">
+        <v>962.384268884</v>
+      </c>
       <c r="AM42" t="n">
         <v>3088.32321525</v>
       </c>
-      <c r="AN42" t="inlineStr"/>
-      <c r="AO42" t="inlineStr"/>
+      <c r="AN42" t="n">
+        <v>3.209033350920502</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0.4285883475937811</v>
+      </c>
       <c r="AP42" t="n">
         <v>22.92953004990827</v>
       </c>
@@ -11336,7 +11390,7 @@
         <v>1781.48985339</v>
       </c>
       <c r="K43" t="n">
-        <v>-52349.024396</v>
+        <v>-52.349024396</v>
       </c>
       <c r="L43" t="n">
         <v>1948.82249193</v>
@@ -11396,12 +11450,18 @@
       <c r="AK43" t="n">
         <v>4.53941845037895</v>
       </c>
-      <c r="AL43" t="inlineStr"/>
+      <c r="AL43" t="n">
+        <v>960.650975604</v>
+      </c>
       <c r="AM43" t="n">
         <v>2961.82249193</v>
       </c>
-      <c r="AN43" t="inlineStr"/>
-      <c r="AO43" t="inlineStr"/>
+      <c r="AN43" t="n">
+        <v>3.083141085728647</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0.4353538353188192</v>
+      </c>
       <c r="AP43" t="n">
         <v>21.47955365507267</v>
       </c>
@@ -11567,7 +11627,7 @@
         <v>1839.49337931</v>
       </c>
       <c r="K44" t="n">
-        <v>-56223.70881</v>
+        <v>-56.22370881</v>
       </c>
       <c r="L44" t="n">
         <v>1907.2731377</v>
@@ -11627,12 +11687,18 @@
       <c r="AK44" t="n">
         <v>4.661451409354044</v>
       </c>
-      <c r="AL44" t="inlineStr"/>
+      <c r="AL44" t="n">
+        <v>956.7762911900001</v>
+      </c>
       <c r="AM44" t="n">
         <v>2920.2731377</v>
       </c>
-      <c r="AN44" t="inlineStr"/>
-      <c r="AO44" t="inlineStr"/>
+      <c r="AN44" t="n">
+        <v>3.052200566203288</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0.4512066176176181</v>
+      </c>
       <c r="AP44" t="n">
         <v>20.39642628285346</v>
       </c>
@@ -11798,7 +11864,7 @@
         <v>1892.68460745</v>
       </c>
       <c r="K45" t="n">
-        <v>-59744.745134</v>
+        <v>-59.744745134</v>
       </c>
       <c r="L45" t="n">
         <v>1843.18901205</v>
@@ -11858,12 +11924,18 @@
       <c r="AK45" t="n">
         <v>4.781434388071472</v>
       </c>
-      <c r="AL45" t="inlineStr"/>
+      <c r="AL45" t="n">
+        <v>953.255254866</v>
+      </c>
       <c r="AM45" t="n">
         <v>2856.18901205</v>
       </c>
-      <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="inlineStr"/>
+      <c r="AN45" t="n">
+        <v>2.99624785436037</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0.4661532957597179</v>
+      </c>
       <c r="AP45" t="n">
         <v>19.38173013602609</v>
       </c>
@@ -12029,7 +12101,7 @@
         <v>1908.93856817</v>
       </c>
       <c r="K46" t="n">
-        <v>-61101.239588</v>
+        <v>-61.101239588</v>
       </c>
       <c r="L46" t="n">
         <v>1732.96191261</v>
@@ -12089,12 +12161,18 @@
       <c r="AK46" t="n">
         <v>4.992819715436103</v>
       </c>
-      <c r="AL46" t="inlineStr"/>
+      <c r="AL46" t="n">
+        <v>951.898760412</v>
+      </c>
       <c r="AM46" t="n">
         <v>2745.96191261</v>
       </c>
-      <c r="AN46" t="inlineStr"/>
-      <c r="AO46" t="inlineStr"/>
+      <c r="AN46" t="n">
+        <v>2.884720546774842</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0.4707400432434641</v>
+      </c>
       <c r="AP46" t="n">
         <v>17.7864032469237</v>
       </c>
@@ -12260,7 +12338,7 @@
         <v>1891.49993162</v>
       </c>
       <c r="K47" t="n">
-        <v>-59840.251557</v>
+        <v>-59.840251557</v>
       </c>
       <c r="L47" t="n">
         <v>1573.79342815</v>
@@ -12320,12 +12398,18 @@
       <c r="AK47" t="n">
         <v>5.418830127923191</v>
       </c>
-      <c r="AL47" t="inlineStr"/>
+      <c r="AL47" t="n">
+        <v>953.159748443</v>
+      </c>
       <c r="AM47" t="n">
         <v>2586.79342815</v>
       </c>
-      <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="inlineStr"/>
+      <c r="AN47" t="n">
+        <v>2.713913834879792</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0.4658300275740023</v>
+      </c>
       <c r="AP47" t="n">
         <v>15.46396354746599</v>
       </c>
@@ -12491,7 +12575,7 @@
         <v>1858.31468039</v>
       </c>
       <c r="K48" t="n">
-        <v>-57248.708655</v>
+        <v>-57.248708655</v>
       </c>
       <c r="L48" t="n">
         <v>1398.04665022</v>
@@ -12551,12 +12635,18 @@
       <c r="AK48" t="n">
         <v>6.439845477320818</v>
       </c>
-      <c r="AL48" t="inlineStr"/>
+      <c r="AL48" t="n">
+        <v>955.751291345</v>
+      </c>
       <c r="AM48" t="n">
         <v>2411.04665022</v>
       </c>
-      <c r="AN48" t="inlineStr"/>
-      <c r="AO48" t="inlineStr"/>
+      <c r="AN48" t="n">
+        <v>2.522671611384387</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0.4564978083548263</v>
+      </c>
       <c r="AP48" t="n">
         <v>12.20324586566815</v>
       </c>
